--- a/GITT_charging_potential_detection.xlsx
+++ b/GITT_charging_potential_detection.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:J150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,2914 +482,4770 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>407856.5162517744</v>
+        <v>438370.7857168392</v>
       </c>
       <c r="B2" t="n">
-        <v>408456.467804772</v>
+        <v>434775.6683954172</v>
       </c>
       <c r="C2" t="n">
-        <v>408471.5165935608</v>
+        <v>434810.6459693496</v>
       </c>
       <c r="D2" t="n">
-        <v>412031.6563410468</v>
+        <v>442560.7825950456</v>
       </c>
       <c r="E2" t="n">
-        <v>1.36327230930328</v>
+        <v>2.14767479896545</v>
       </c>
       <c r="F2" t="n">
-        <v>2.36526918411254</v>
+        <v>2.38422536849975</v>
       </c>
       <c r="G2" t="n">
-        <v>2.30429697036743</v>
+        <v>2.36855411529541</v>
       </c>
       <c r="H2" t="n">
-        <v>2.09219169616699</v>
+        <v>2.1572368144989</v>
       </c>
       <c r="I2" t="n">
-        <v>13.9218818750592</v>
+        <v>13.1312902821047</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>13.943056387165</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>412051.6571261472</v>
+        <v>442600.7841652428</v>
       </c>
       <c r="B3" t="n">
-        <v>412646.488882956</v>
+        <v>439005.5948438712</v>
       </c>
       <c r="C3" t="n">
-        <v>412661.5134717708</v>
+        <v>439040.6444177532</v>
       </c>
       <c r="D3" t="n">
-        <v>416221.6532192496</v>
+        <v>446750.7794732484</v>
       </c>
       <c r="E3" t="n">
-        <v>2.09209632873535</v>
+        <v>2.1569697856903</v>
       </c>
       <c r="F3" t="n">
-        <v>2.51829195022583</v>
+        <v>2.34425950050354</v>
       </c>
       <c r="G3" t="n">
-        <v>2.47820353507995</v>
+        <v>2.28961658477783</v>
       </c>
       <c r="H3" t="n">
-        <v>2.19111442565918</v>
+        <v>2.16326808929443</v>
       </c>
       <c r="I3" t="n">
-        <v>27.6132629619746</v>
+        <v>27.7716468701849</v>
       </c>
       <c r="J3" t="n">
-        <v>13.9218818750592</v>
+        <v>27.8872908197837</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>416241.65400435</v>
+        <v>446790.7810434456</v>
       </c>
       <c r="B4" t="n">
-        <v>416856.462346278</v>
+        <v>443195.6159220516</v>
       </c>
       <c r="C4" t="n">
-        <v>416871.511135074</v>
+        <v>443230.6412959596</v>
       </c>
       <c r="D4" t="n">
-        <v>420431.6508825492</v>
+        <v>450940.7763514512</v>
       </c>
       <c r="E4" t="n">
-        <v>2.19090437889099</v>
+        <v>2.16294360160827</v>
       </c>
       <c r="F4" t="n">
-        <v>2.54919815063476</v>
+        <v>2.31773018836975</v>
       </c>
       <c r="G4" t="n">
-        <v>2.48314785957336</v>
+        <v>2.27978730201721</v>
       </c>
       <c r="H4" t="n">
-        <v>2.21432733535766</v>
+        <v>2.16823029518127</v>
       </c>
       <c r="I4" t="n">
-        <v>41.7673078318881</v>
+        <v>41.4834267317349</v>
       </c>
       <c r="J4" t="n">
-        <v>27.8447573732369</v>
+        <v>41.8314823778621</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>420451.6516676496</v>
+        <v>450980.7779216484</v>
       </c>
       <c r="B5" t="n">
-        <v>421046.4834244692</v>
+        <v>447385.612800258</v>
       </c>
       <c r="C5" t="n">
-        <v>421061.5080132804</v>
+        <v>447420.6381741696</v>
       </c>
       <c r="D5" t="n">
-        <v>424621.647760752</v>
+        <v>455130.7732296504</v>
       </c>
       <c r="E5" t="n">
-        <v>2.21411728858947</v>
+        <v>2.16800141334533</v>
       </c>
       <c r="F5" t="n">
-        <v>2.55593681335449</v>
+        <v>2.30122089385986</v>
       </c>
       <c r="G5" t="n">
-        <v>2.51752829551696</v>
+        <v>2.27749705314636</v>
       </c>
       <c r="H5" t="n">
-        <v>2.22295594215393</v>
+        <v>2.17265820503234</v>
       </c>
       <c r="I5" t="n">
-        <v>55.4586816893895</v>
+        <v>55.1952419913054</v>
       </c>
       <c r="J5" t="n">
-        <v>41.7673078318881</v>
+        <v>55.7757127597642</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>424641.6485458488</v>
+        <v>455170.7747998512</v>
       </c>
       <c r="B6" t="n">
-        <v>425256.456887784</v>
+        <v>451575.6096784644</v>
       </c>
       <c r="C6" t="n">
-        <v>425271.50567658</v>
+        <v>451610.635052376</v>
       </c>
       <c r="D6" t="n">
-        <v>428831.6454240552</v>
+        <v>459360.771678054</v>
       </c>
       <c r="E6" t="n">
-        <v>2.22297501564025</v>
+        <v>2.17265820503234</v>
       </c>
       <c r="F6" t="n">
-        <v>2.55782651901245</v>
+        <v>2.29148697853088</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4930362701416</v>
+        <v>2.28622484207153</v>
       </c>
       <c r="H6" t="n">
-        <v>2.22837734222412</v>
+        <v>2.17615103721618</v>
       </c>
       <c r="I6" t="n">
-        <v>69.61261027422459</v>
+        <v>68.9071115402885</v>
       </c>
       <c r="J6" t="n">
-        <v>55.6901623509136</v>
+        <v>69.7199987483633</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>428851.646209152</v>
+        <v>459400.7732482476</v>
       </c>
       <c r="B7" t="n">
-        <v>429446.4779659788</v>
+        <v>455805.5839268796</v>
       </c>
       <c r="C7" t="n">
-        <v>429461.5025547792</v>
+        <v>455840.633500776</v>
       </c>
       <c r="D7" t="n">
-        <v>433021.6423022616</v>
+        <v>463550.7685562604</v>
       </c>
       <c r="E7" t="n">
-        <v>2.22839641571044</v>
+        <v>2.17613196372985</v>
       </c>
       <c r="F7" t="n">
-        <v>2.55509686470031</v>
+        <v>2.28629565238952</v>
       </c>
       <c r="G7" t="n">
-        <v>2.51842546463012</v>
+        <v>2.25844931602478</v>
       </c>
       <c r="H7" t="n">
-        <v>2.231947183609</v>
+        <v>2.17960548400878</v>
       </c>
       <c r="I7" t="n">
-        <v>83.3037950104473</v>
+        <v>83.54865385703771</v>
       </c>
       <c r="J7" t="n">
-        <v>69.61261027422459</v>
+        <v>83.6642978661431</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>433041.6430873584</v>
+        <v>463590.770126454</v>
       </c>
       <c r="B8" t="n">
-        <v>433656.4514292936</v>
+        <v>459995.6050050744</v>
       </c>
       <c r="C8" t="n">
-        <v>433671.5002180824</v>
+        <v>460030.6303789788</v>
       </c>
       <c r="D8" t="n">
-        <v>437231.6399655648</v>
+        <v>467740.7654344668</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2320806980133</v>
+        <v>2.17943382263183</v>
       </c>
       <c r="F8" t="n">
-        <v>2.54725098609924</v>
+        <v>2.28413891792297</v>
       </c>
       <c r="G8" t="n">
-        <v>2.48309063911438</v>
+        <v>2.2634117603302</v>
       </c>
       <c r="H8" t="n">
-        <v>2.23471498489379</v>
+        <v>2.18201041221618</v>
       </c>
       <c r="I8" t="n">
-        <v>97.45751725795949</v>
+        <v>97.2605496997575</v>
       </c>
       <c r="J8" t="n">
-        <v>83.53529078211901</v>
+        <v>97.6086079783655</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>437251.6407506652</v>
+        <v>467780.7670046604</v>
       </c>
       <c r="B9" t="n">
-        <v>437846.4725074812</v>
+        <v>464185.6018832808</v>
       </c>
       <c r="C9" t="n">
-        <v>437861.4970962816</v>
+        <v>464220.6272571816</v>
       </c>
       <c r="D9" t="n">
-        <v>441421.6368437712</v>
+        <v>471930.7623126731</v>
       </c>
       <c r="E9" t="n">
-        <v>2.23469591140747</v>
+        <v>2.18201041221618</v>
       </c>
       <c r="F9" t="n">
-        <v>2.54160046577453</v>
+        <v>2.28358554840087</v>
       </c>
       <c r="G9" t="n">
-        <v>2.50636076927185</v>
+        <v>2.27001547813415</v>
       </c>
       <c r="H9" t="n">
-        <v>2.23683404922485</v>
+        <v>2.18536949157714</v>
       </c>
       <c r="I9" t="n">
-        <v>111.147628311811</v>
+        <v>110.972285252484</v>
       </c>
       <c r="J9" t="n">
-        <v>97.45751725795949</v>
+        <v>111.552750503914</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>441441.6376288716</v>
+        <v>471970.7638828668</v>
       </c>
       <c r="B10" t="n">
-        <v>442056.4459708068</v>
+        <v>468375.59876148</v>
       </c>
       <c r="C10" t="n">
-        <v>442071.4947595848</v>
+        <v>468410.6241353808</v>
       </c>
       <c r="D10" t="n">
-        <v>445631.634507078</v>
+        <v>476160.7607610732</v>
       </c>
       <c r="E10" t="n">
-        <v>2.23679590225219</v>
+        <v>2.18517875671386</v>
       </c>
       <c r="F10" t="n">
-        <v>2.53495717048645</v>
+        <v>2.28268837928772</v>
       </c>
       <c r="G10" t="n">
-        <v>2.47087311744689</v>
+        <v>2.27989172935485</v>
       </c>
       <c r="H10" t="n">
-        <v>2.2382276058197</v>
+        <v>2.18842315673828</v>
       </c>
       <c r="I10" t="n">
-        <v>125.300745915334</v>
+        <v>124.684056981641</v>
       </c>
       <c r="J10" t="n">
-        <v>111.379101568829</v>
+        <v>125.496933017833</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>445651.6352921748</v>
+        <v>476200.7623312704</v>
       </c>
       <c r="B11" t="n">
-        <v>446246.4670489872</v>
+        <v>472605.5730099024</v>
       </c>
       <c r="C11" t="n">
-        <v>446261.4916377876</v>
+        <v>472640.6225837808</v>
       </c>
       <c r="D11" t="n">
-        <v>449821.6313852844</v>
+        <v>480350.7576392833</v>
       </c>
       <c r="E11" t="n">
-        <v>2.23813223838806</v>
+        <v>2.18846130371093</v>
       </c>
       <c r="F11" t="n">
-        <v>2.52690124511718</v>
+        <v>2.28671550750732</v>
       </c>
       <c r="G11" t="n">
-        <v>2.49313163757324</v>
+        <v>2.26524400711059</v>
       </c>
       <c r="H11" t="n">
-        <v>2.23931574821472</v>
+        <v>2.19222140312194</v>
       </c>
       <c r="I11" t="n">
-        <v>138.99085556516</v>
+        <v>139.32546941069</v>
       </c>
       <c r="J11" t="n">
-        <v>125.300745915334</v>
+        <v>139.441112732333</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>449841.6321703848</v>
+        <v>480390.7592094768</v>
       </c>
       <c r="B12" t="n">
-        <v>450456.4405123128</v>
+        <v>476795.5940880828</v>
       </c>
       <c r="C12" t="n">
-        <v>450471.4893010944</v>
+        <v>476830.6194619836</v>
       </c>
       <c r="D12" t="n">
-        <v>454031.629048584</v>
+        <v>484540.754517486</v>
       </c>
       <c r="E12" t="n">
-        <v>2.23933482170105</v>
+        <v>2.19208765029907</v>
       </c>
       <c r="F12" t="n">
-        <v>2.52136540412902</v>
+        <v>2.28952121734619</v>
       </c>
       <c r="G12" t="n">
-        <v>2.45772051811218</v>
+        <v>2.27318358421325</v>
       </c>
       <c r="H12" t="n">
-        <v>2.24015569686889</v>
+        <v>2.19548511505127</v>
       </c>
       <c r="I12" t="n">
-        <v>153.14357178785</v>
+        <v>153.037301045346</v>
       </c>
       <c r="J12" t="n">
-        <v>139.222328934157</v>
+        <v>153.385357273157</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>454051.6298336844</v>
+        <v>484580.7560876832</v>
       </c>
       <c r="B13" t="n">
-        <v>454646.4615904932</v>
+        <v>480985.5909662892</v>
       </c>
       <c r="C13" t="n">
-        <v>454661.4861793008</v>
+        <v>481020.6163401864</v>
       </c>
       <c r="D13" t="n">
-        <v>458221.6259267904</v>
+        <v>488730.7513956888</v>
       </c>
       <c r="E13" t="n">
-        <v>2.24013662338256</v>
+        <v>2.1954276561737</v>
       </c>
       <c r="F13" t="n">
-        <v>2.51371049880981</v>
+        <v>2.29249858856201</v>
       </c>
       <c r="G13" t="n">
-        <v>2.48123884201049</v>
+        <v>2.28188681602478</v>
       </c>
       <c r="H13" t="n">
-        <v>2.24097657203674</v>
+        <v>2.1984052658081</v>
       </c>
       <c r="I13" t="n">
-        <v>166.8340560482</v>
+        <v>166.749141398135</v>
       </c>
       <c r="J13" t="n">
-        <v>153.14357178785</v>
+        <v>167.329611990823</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>458241.6267118872</v>
+        <v>488770.752965886</v>
       </c>
       <c r="B14" t="n">
-        <v>458856.4350538188</v>
+        <v>485175.5878444921</v>
       </c>
       <c r="C14" t="n">
-        <v>458871.4838426076</v>
+        <v>485210.6132183964</v>
       </c>
       <c r="D14" t="n">
-        <v>462431.62359009</v>
+        <v>492960.7498440888</v>
       </c>
       <c r="E14" t="n">
-        <v>2.24105286598205</v>
+        <v>2.19827151298522</v>
       </c>
       <c r="F14" t="n">
-        <v>2.50987339019775</v>
+        <v>2.29490327835083</v>
       </c>
       <c r="G14" t="n">
-        <v>2.44659113883972</v>
+        <v>2.29287838935852</v>
       </c>
       <c r="H14" t="n">
-        <v>2.24175930023193</v>
+        <v>2.20121073722839</v>
       </c>
       <c r="I14" t="n">
-        <v>180.987422406575</v>
+        <v>180.461013907446</v>
       </c>
       <c r="J14" t="n">
-        <v>167.065522876531</v>
+        <v>181.273897212077</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>462451.6243751904</v>
+        <v>493000.751414286</v>
       </c>
       <c r="B15" t="n">
-        <v>463046.4561320028</v>
+        <v>489405.5620929144</v>
       </c>
       <c r="C15" t="n">
-        <v>463061.480720814</v>
+        <v>489440.6116668</v>
       </c>
       <c r="D15" t="n">
-        <v>466621.6204682929</v>
+        <v>497150.7467222916</v>
       </c>
       <c r="E15" t="n">
-        <v>2.24168276786804</v>
+        <v>2.20098185539245</v>
       </c>
       <c r="F15" t="n">
-        <v>2.50315380096435</v>
+        <v>2.29747986793518</v>
       </c>
       <c r="G15" t="n">
-        <v>2.47165584564209</v>
+        <v>2.27952003479003</v>
       </c>
       <c r="H15" t="n">
-        <v>2.24237012863159</v>
+        <v>2.20373010635376</v>
       </c>
       <c r="I15" t="n">
-        <v>194.677903737647</v>
+        <v>195.102499718503</v>
       </c>
       <c r="J15" t="n">
-        <v>180.987422406575</v>
+        <v>195.218144263387</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>466641.6212533932</v>
+        <v>497190.7482924887</v>
       </c>
       <c r="B16" t="n">
-        <v>467256.4295953176</v>
+        <v>493595.5831710984</v>
       </c>
       <c r="C16" t="n">
-        <v>467271.4783841172</v>
+        <v>493630.6085450064</v>
       </c>
       <c r="D16" t="n">
-        <v>470831.6181315924</v>
+        <v>501340.7436004943</v>
       </c>
       <c r="E16" t="n">
-        <v>2.24235105514526</v>
+        <v>2.20376825332641</v>
       </c>
       <c r="F16" t="n">
-        <v>2.50107312202453</v>
+        <v>2.29921674728393</v>
       </c>
       <c r="G16" t="n">
-        <v>2.43813443183898</v>
+        <v>2.28541779518127</v>
       </c>
       <c r="H16" t="n">
-        <v>2.24292373657226</v>
+        <v>2.20653581619262</v>
       </c>
       <c r="I16" t="n">
-        <v>208.831072653023</v>
+        <v>208.814363344217</v>
       </c>
       <c r="J16" t="n">
-        <v>194.909375622894</v>
+        <v>209.162421541758</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>470851.6189166928</v>
+        <v>501380.7451706916</v>
       </c>
       <c r="B17" t="n">
-        <v>471446.4506735124</v>
+        <v>497785.5800493048</v>
       </c>
       <c r="C17" t="n">
-        <v>471461.4752623236</v>
+        <v>497820.6054232128</v>
       </c>
       <c r="D17" t="n">
-        <v>475021.6150097952</v>
+        <v>505530.7404786972</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2428662776947</v>
+        <v>2.20651674270629</v>
       </c>
       <c r="F17" t="n">
-        <v>2.49366617202758</v>
+        <v>2.30101084709167</v>
       </c>
       <c r="G17" t="n">
-        <v>2.46335196495056</v>
+        <v>2.29181146621704</v>
       </c>
       <c r="H17" t="n">
-        <v>2.24332451820373</v>
+        <v>2.20922684669494</v>
       </c>
       <c r="I17" t="n">
-        <v>222.522105309947</v>
+        <v>222.526164641363</v>
       </c>
       <c r="J17" t="n">
-        <v>208.831072653023</v>
+        <v>223.106632967552</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>475041.615794892</v>
+        <v>505570.7420488907</v>
       </c>
       <c r="B18" t="n">
-        <v>475656.4241368272</v>
+        <v>501975.5769275112</v>
       </c>
       <c r="C18" t="n">
-        <v>475671.4729256196</v>
+        <v>502010.6023014192</v>
       </c>
       <c r="D18" t="n">
-        <v>479231.6126731019</v>
+        <v>509760.7389270972</v>
       </c>
       <c r="E18" t="n">
-        <v>2.24334359169006</v>
+        <v>2.20894050598144</v>
       </c>
       <c r="F18" t="n">
-        <v>2.49253988265991</v>
+        <v>2.30232787132263</v>
       </c>
       <c r="G18" t="n">
-        <v>2.42973494529724</v>
+        <v>2.30113554000854</v>
       </c>
       <c r="H18" t="n">
-        <v>2.24403095245361</v>
+        <v>2.21170806884765</v>
       </c>
       <c r="I18" t="n">
-        <v>236.675772151729</v>
+        <v>236.237963681857</v>
       </c>
       <c r="J18" t="n">
-        <v>222.753588030065</v>
+        <v>237.050843701093</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>479251.6134581988</v>
+        <v>509800.7404972944</v>
       </c>
       <c r="B19" t="n">
-        <v>479846.4452150256</v>
+        <v>506205.5511759228</v>
       </c>
       <c r="C19" t="n">
-        <v>479861.4698038225</v>
+        <v>506240.6007498192</v>
       </c>
       <c r="D19" t="n">
-        <v>483421.6095513084</v>
+        <v>513950.7358053036</v>
       </c>
       <c r="E19" t="n">
-        <v>2.24391627311706</v>
+        <v>2.21142172813415</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4863166809082</v>
+        <v>2.30488538742065</v>
       </c>
       <c r="G19" t="n">
-        <v>2.45647954940795</v>
+        <v>2.28957843780517</v>
       </c>
       <c r="H19" t="n">
-        <v>2.24424076080322</v>
+        <v>2.21409368515014</v>
       </c>
       <c r="I19" t="n">
-        <v>250.366005923464</v>
+        <v>250.879395688618</v>
       </c>
       <c r="J19" t="n">
-        <v>236.675772151729</v>
+        <v>250.995039245634</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>483441.6103364052</v>
+        <v>513990.7373755008</v>
       </c>
       <c r="B20" t="n">
-        <v>484056.4186783404</v>
+        <v>510395.5722541211</v>
       </c>
       <c r="C20" t="n">
-        <v>484071.467467122</v>
+        <v>510430.597628022</v>
       </c>
       <c r="D20" t="n">
-        <v>487631.6072146116</v>
+        <v>518140.73268351</v>
       </c>
       <c r="E20" t="n">
-        <v>2.24424076080322</v>
+        <v>2.21407461166381</v>
       </c>
       <c r="F20" t="n">
-        <v>2.48788213729858</v>
+        <v>2.30648851394653</v>
       </c>
       <c r="G20" t="n">
-        <v>2.42486715316772</v>
+        <v>2.29490327835083</v>
       </c>
       <c r="H20" t="n">
-        <v>2.24488997459411</v>
+        <v>2.21676588058471</v>
       </c>
       <c r="I20" t="n">
-        <v>264.519416064172</v>
+        <v>264.591212534482</v>
       </c>
       <c r="J20" t="n">
-        <v>250.597482105686</v>
+        <v>264.939270878771</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>487651.6079997084</v>
+        <v>518180.7342537072</v>
       </c>
       <c r="B21" t="n">
-        <v>488246.4397565243</v>
+        <v>514585.569132324</v>
       </c>
       <c r="C21" t="n">
-        <v>488261.4643453284</v>
+        <v>514620.5945062212</v>
       </c>
       <c r="D21" t="n">
-        <v>491821.6040928217</v>
+        <v>522330.72956172</v>
       </c>
       <c r="E21" t="n">
-        <v>2.24473714828491</v>
+        <v>2.21634578704834</v>
       </c>
       <c r="F21" t="n">
-        <v>2.48519039154052</v>
+        <v>2.30778622627258</v>
       </c>
       <c r="G21" t="n">
-        <v>2.4558687210083</v>
+        <v>2.3001902103424</v>
       </c>
       <c r="H21" t="n">
-        <v>2.2452335357666</v>
+        <v>2.21913242340087</v>
       </c>
       <c r="I21" t="n">
-        <v>278.209507719801</v>
+        <v>278.302982983908</v>
       </c>
       <c r="J21" t="n">
-        <v>264.519416064172</v>
+        <v>278.883451930698</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>491841.6048779184</v>
+        <v>522370.7311319136</v>
       </c>
       <c r="B22" t="n">
-        <v>492456.4132198536</v>
+        <v>518775.5660105232</v>
       </c>
       <c r="C22" t="n">
-        <v>492471.462008628</v>
+        <v>518810.5913844241</v>
       </c>
       <c r="D22" t="n">
-        <v>496031.6017561248</v>
+        <v>526560.726926394</v>
       </c>
       <c r="E22" t="n">
-        <v>2.2452335357666</v>
+        <v>2.21896076202392</v>
       </c>
       <c r="F22" t="n">
-        <v>2.48719477653503</v>
+        <v>2.30889320373535</v>
       </c>
       <c r="G22" t="n">
-        <v>2.42385530471801</v>
+        <v>2.308189868927</v>
       </c>
       <c r="H22" t="n">
-        <v>2.24557709693908</v>
+        <v>2.22102189064025</v>
       </c>
       <c r="I22" t="n">
-        <v>292.362319433219</v>
+        <v>292.014828663924</v>
       </c>
       <c r="J22" t="n">
-        <v>278.44098164356</v>
+        <v>292.827708673917</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>496051.6025412216</v>
+        <v>526600.7284775148</v>
       </c>
       <c r="B23" t="n">
-        <v>496646.434298034</v>
+        <v>523005.5402589492</v>
       </c>
       <c r="C23" t="n">
-        <v>496661.4588868344</v>
+        <v>523040.589832824</v>
       </c>
       <c r="D23" t="n">
-        <v>500221.5986343276</v>
+        <v>530750.7218066545</v>
       </c>
       <c r="E23" t="n">
-        <v>2.24559617042541</v>
+        <v>2.22079300880432</v>
       </c>
       <c r="F23" t="n">
-        <v>2.48394966125488</v>
+        <v>2.31137442588806</v>
       </c>
       <c r="G23" t="n">
-        <v>2.45485687255859</v>
+        <v>2.29830074310302</v>
       </c>
       <c r="H23" t="n">
-        <v>2.24607348442077</v>
+        <v>2.22247242927551</v>
       </c>
       <c r="I23" t="n">
-        <v>306.052838745873</v>
+        <v>306.656318272297</v>
       </c>
       <c r="J23" t="n">
-        <v>292.362319433219</v>
+        <v>306.771962353789</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>500241.599419428</v>
+        <v>530790.7233577751</v>
       </c>
       <c r="B24" t="n">
-        <v>500856.407761356</v>
+        <v>527195.5599506976</v>
       </c>
       <c r="C24" t="n">
-        <v>500871.4565501412</v>
+        <v>527230.5853079052</v>
       </c>
       <c r="D24" t="n">
-        <v>504431.5962976307</v>
+        <v>534940.7166869148</v>
       </c>
       <c r="E24" t="n">
-        <v>2.24601626396179</v>
+        <v>2.22218608856201</v>
       </c>
       <c r="F24" t="n">
-        <v>2.48748111724853</v>
+        <v>2.31059193611145</v>
       </c>
       <c r="G24" t="n">
-        <v>2.42368364334106</v>
+        <v>2.3006100654602</v>
       </c>
       <c r="H24" t="n">
-        <v>2.24634075164794</v>
+        <v>2.2247245311737</v>
       </c>
       <c r="I24" t="n">
-        <v>320.206112119042</v>
+        <v>320.368075126219</v>
       </c>
       <c r="J24" t="n">
-        <v>306.284307047732</v>
+        <v>320.716128749253</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>504451.5970827276</v>
+        <v>534980.7182380356</v>
       </c>
       <c r="B25" t="n">
-        <v>505046.4288395364</v>
+        <v>531385.5548309436</v>
       </c>
       <c r="C25" t="n">
-        <v>505061.4534283475</v>
+        <v>531420.5801881655</v>
       </c>
       <c r="D25" t="n">
-        <v>508621.5931758336</v>
+        <v>539130.7115671716</v>
       </c>
       <c r="E25" t="n">
-        <v>2.24635982513427</v>
+        <v>2.22462916374206</v>
       </c>
       <c r="F25" t="n">
-        <v>2.48484683036804</v>
+        <v>2.3120424747467</v>
       </c>
       <c r="G25" t="n">
-        <v>2.45556330680847</v>
+        <v>2.30540060997009</v>
       </c>
       <c r="H25" t="n">
-        <v>2.24660801887512</v>
+        <v>2.22739672660827</v>
       </c>
       <c r="I25" t="n">
-        <v>333.896740273349</v>
+        <v>334.079825968864</v>
       </c>
       <c r="J25" t="n">
-        <v>320.206112119042</v>
+        <v>334.660292179933</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>508641.593960934</v>
+        <v>539170.713118296</v>
       </c>
       <c r="B26" t="n">
-        <v>509256.402302862</v>
+        <v>535575.5497112039</v>
       </c>
       <c r="C26" t="n">
-        <v>509271.4510916544</v>
+        <v>535610.5750684224</v>
       </c>
       <c r="D26" t="n">
-        <v>512831.5908391367</v>
+        <v>543360.7079985528</v>
       </c>
       <c r="E26" t="n">
-        <v>2.24670338630676</v>
+        <v>2.22701478004455</v>
       </c>
       <c r="F26" t="n">
-        <v>2.48889374732971</v>
+        <v>2.31286311149597</v>
       </c>
       <c r="G26" t="n">
-        <v>2.42418003082275</v>
+        <v>2.31171727180481</v>
       </c>
       <c r="H26" t="n">
-        <v>2.24697065353393</v>
+        <v>2.22983956336975</v>
       </c>
       <c r="I26" t="n">
-        <v>348.049658082523</v>
+        <v>347.791523537538</v>
       </c>
       <c r="J26" t="n">
-        <v>334.128225268065</v>
+        <v>348.604398554797</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>512851.5916242336</v>
+        <v>543400.7095496736</v>
       </c>
       <c r="B27" t="n">
-        <v>513446.4233810496</v>
+        <v>539805.5219426256</v>
       </c>
       <c r="C27" t="n">
-        <v>513461.4479698608</v>
+        <v>539840.5714998036</v>
       </c>
       <c r="D27" t="n">
-        <v>517021.587717336</v>
+        <v>547550.7028788131</v>
       </c>
       <c r="E27" t="n">
-        <v>2.24706602096557</v>
+        <v>2.22961068153381</v>
       </c>
       <c r="F27" t="n">
-        <v>2.4861831665039</v>
+        <v>2.31559252738952</v>
       </c>
       <c r="G27" t="n">
-        <v>2.45668959617614</v>
+        <v>2.30440807342529</v>
       </c>
       <c r="H27" t="n">
-        <v>2.24710440635681</v>
+        <v>2.23237800598144</v>
       </c>
       <c r="I27" t="n">
-        <v>361.740233281005</v>
+        <v>362.432865842825</v>
       </c>
       <c r="J27" t="n">
-        <v>348.049658082523</v>
+        <v>362.548508425566</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>517041.5885024364</v>
+        <v>547590.704429934</v>
       </c>
       <c r="B28" t="n">
-        <v>517656.3968443644</v>
+        <v>543995.5410228421</v>
       </c>
       <c r="C28" t="n">
-        <v>517671.4456331676</v>
+        <v>544030.5663800532</v>
       </c>
       <c r="D28" t="n">
-        <v>521231.5853806356</v>
+        <v>551740.69775907</v>
       </c>
       <c r="E28" t="n">
-        <v>2.24714255332946</v>
+        <v>2.23216819763183</v>
       </c>
       <c r="F28" t="n">
-        <v>2.4891037940979</v>
+        <v>2.31671857833862</v>
       </c>
       <c r="G28" t="n">
-        <v>2.42383623123168</v>
+        <v>2.30811071395874</v>
       </c>
       <c r="H28" t="n">
-        <v>2.24750518798828</v>
+        <v>2.23428654670715</v>
       </c>
       <c r="I28" t="n">
-        <v>375.894172157975</v>
+        <v>376.144595949152</v>
       </c>
       <c r="J28" t="n">
-        <v>361.971709151858</v>
+        <v>376.492649172734</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>521251.586165736</v>
+        <v>551780.6993101944</v>
       </c>
       <c r="B29" t="n">
-        <v>521846.4179225593</v>
+        <v>548185.5359031024</v>
       </c>
       <c r="C29" t="n">
-        <v>521861.4425113668</v>
+        <v>548220.5612603064</v>
       </c>
       <c r="D29" t="n">
-        <v>525421.5817183199</v>
+        <v>555930.6926393232</v>
       </c>
       <c r="E29" t="n">
-        <v>2.24744796752929</v>
+        <v>2.23396205902099</v>
       </c>
       <c r="F29" t="n">
-        <v>2.48944735527038</v>
+        <v>2.3177683353424</v>
       </c>
       <c r="G29" t="n">
-        <v>2.45982027053833</v>
+        <v>2.31215691566467</v>
       </c>
       <c r="H29" t="n">
-        <v>2.24784874916076</v>
+        <v>2.23636698722839</v>
       </c>
       <c r="I29" t="n">
-        <v>389.58447579569</v>
+        <v>389.8562235584</v>
       </c>
       <c r="J29" t="n">
-        <v>375.894172157975</v>
+        <v>390.436684628543</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>525441.5824938804</v>
+        <v>555970.6941904477</v>
       </c>
       <c r="B30" t="n">
-        <v>526056.3905426495</v>
+        <v>552375.5307833628</v>
       </c>
       <c r="C30" t="n">
-        <v>526071.4393242564</v>
+        <v>552410.556140556</v>
       </c>
       <c r="D30" t="n">
-        <v>529631.5773741408</v>
+        <v>560160.6890706972</v>
       </c>
       <c r="E30" t="n">
-        <v>2.24781060218811</v>
+        <v>2.23609972000122</v>
       </c>
       <c r="F30" t="n">
-        <v>2.49523162841796</v>
+        <v>2.31769180297851</v>
       </c>
       <c r="G30" t="n">
-        <v>2.42893314361572</v>
+        <v>2.31748914718627</v>
       </c>
       <c r="H30" t="n">
-        <v>2.24823069572448</v>
+        <v>2.23875260353088</v>
       </c>
       <c r="I30" t="n">
-        <v>403.738129760056</v>
+        <v>403.567959065326</v>
       </c>
       <c r="J30" t="n">
-        <v>389.815953349164</v>
+        <v>404.380834319045</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>529651.5781497012</v>
+        <v>560200.6906218216</v>
       </c>
       <c r="B31" t="n">
-        <v>530246.4096228696</v>
+        <v>556605.5030147736</v>
       </c>
       <c r="C31" t="n">
-        <v>530261.4342045096</v>
+        <v>556640.5525719336</v>
       </c>
       <c r="D31" t="n">
-        <v>533821.5722543977</v>
+        <v>564350.683950954</v>
       </c>
       <c r="E31" t="n">
-        <v>2.24805879592895</v>
+        <v>2.23838996887207</v>
       </c>
       <c r="F31" t="n">
-        <v>2.49458265304565</v>
+        <v>2.32019209861755</v>
       </c>
       <c r="G31" t="n">
-        <v>2.46421098709106</v>
+        <v>2.31053471565246</v>
       </c>
       <c r="H31" t="n">
-        <v>2.24849772453308</v>
+        <v>2.24125289916992</v>
       </c>
       <c r="I31" t="n">
-        <v>417.429109952928</v>
+        <v>418.20928563873</v>
       </c>
       <c r="J31" t="n">
-        <v>403.738129760056</v>
+        <v>418.324928574609</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>533841.5730299616</v>
+        <v>564390.6855020784</v>
       </c>
       <c r="B32" t="n">
-        <v>534456.3810787272</v>
+        <v>560795.5220950044</v>
       </c>
       <c r="C32" t="n">
-        <v>534471.4298603196</v>
+        <v>560830.547452194</v>
       </c>
       <c r="D32" t="n">
-        <v>538031.5679102148</v>
+        <v>568540.6788312036</v>
       </c>
       <c r="E32" t="n">
-        <v>2.24840235710144</v>
+        <v>2.24115753173828</v>
       </c>
       <c r="F32" t="n">
-        <v>2.50029039382934</v>
+        <v>2.32137537002563</v>
       </c>
       <c r="G32" t="n">
-        <v>2.43248391151428</v>
+        <v>2.31385564804077</v>
       </c>
       <c r="H32" t="n">
-        <v>2.24857425689697</v>
+        <v>2.2438485622406</v>
       </c>
       <c r="I32" t="n">
-        <v>431.582983517064</v>
+        <v>431.92100610214</v>
       </c>
       <c r="J32" t="n">
-        <v>417.66059761683</v>
+        <v>432.269059146593</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>538051.5686857752</v>
+        <v>568580.680382328</v>
       </c>
       <c r="B33" t="n">
-        <v>538646.4001589508</v>
+        <v>564985.5169752648</v>
       </c>
       <c r="C33" t="n">
-        <v>538661.42474058</v>
+        <v>565020.5423324544</v>
       </c>
       <c r="D33" t="n">
-        <v>542221.5627904681</v>
+        <v>572730.673711464</v>
       </c>
       <c r="E33" t="n">
-        <v>2.24855518341064</v>
+        <v>2.24350500106811</v>
       </c>
       <c r="F33" t="n">
-        <v>2.50025224685668</v>
+        <v>2.32238698005676</v>
       </c>
       <c r="G33" t="n">
-        <v>2.46883058547973</v>
+        <v>2.31746292114257</v>
       </c>
       <c r="H33" t="n">
-        <v>2.24905133247375</v>
+        <v>2.24550914764404</v>
       </c>
       <c r="I33" t="n">
-        <v>445.274131025485</v>
+        <v>445.632800934877</v>
       </c>
       <c r="J33" t="n">
-        <v>431.582983517064</v>
+        <v>446.213268134704</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>542241.5635660284</v>
+        <v>572770.6752625848</v>
       </c>
       <c r="B34" t="n">
-        <v>542856.3716147976</v>
+        <v>569175.5118555216</v>
       </c>
       <c r="C34" t="n">
-        <v>542871.4203964043</v>
+        <v>569210.5372127112</v>
       </c>
       <c r="D34" t="n">
-        <v>546431.5584462852</v>
+        <v>576960.6701428416</v>
       </c>
       <c r="E34" t="n">
-        <v>2.2488796710968</v>
+        <v>2.24510836601257</v>
       </c>
       <c r="F34" t="n">
-        <v>2.50517725944519</v>
+        <v>2.32290244102478</v>
       </c>
       <c r="G34" t="n">
-        <v>2.43620634078979</v>
+        <v>2.32205843925476</v>
       </c>
       <c r="H34" t="n">
-        <v>2.24914693832397</v>
+        <v>2.24799036979675</v>
       </c>
       <c r="I34" t="n">
-        <v>459.427966718682</v>
+        <v>459.344538507293</v>
       </c>
       <c r="J34" t="n">
-        <v>445.505621416872</v>
+        <v>460.157411657084</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>546451.5592218456</v>
+        <v>577000.6716939624</v>
       </c>
       <c r="B35" t="n">
-        <v>547046.3906950356</v>
+        <v>573405.4840869145</v>
       </c>
       <c r="C35" t="n">
-        <v>547061.4152766648</v>
+        <v>573440.5336440924</v>
       </c>
       <c r="D35" t="n">
-        <v>550621.5533265348</v>
+        <v>581150.665023102</v>
       </c>
       <c r="E35" t="n">
-        <v>2.24920415878295</v>
+        <v>2.24772310256958</v>
       </c>
       <c r="F35" t="n">
-        <v>2.50527286529541</v>
+        <v>2.32479190826416</v>
       </c>
       <c r="G35" t="n">
-        <v>2.47318315505981</v>
+        <v>2.31626057624816</v>
       </c>
       <c r="H35" t="n">
-        <v>2.24947142601013</v>
+        <v>2.25073862075805</v>
       </c>
       <c r="I35" t="n">
-        <v>473.11881997051</v>
+        <v>473.98593236496</v>
       </c>
       <c r="J35" t="n">
-        <v>459.427966718682</v>
+        <v>474.101575674925</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>550641.5541020952</v>
+        <v>581190.6665742229</v>
       </c>
       <c r="B36" t="n">
-        <v>551256.3621508644</v>
+        <v>577595.5031671524</v>
       </c>
       <c r="C36" t="n">
-        <v>551271.410932482</v>
+        <v>577630.5285243528</v>
       </c>
       <c r="D36" t="n">
-        <v>554831.5489823556</v>
+        <v>585340.659903366</v>
       </c>
       <c r="E36" t="n">
-        <v>2.24954771995544</v>
+        <v>2.25037598609924</v>
       </c>
       <c r="F36" t="n">
-        <v>2.51063704490661</v>
+        <v>2.32605147361755</v>
       </c>
       <c r="G36" t="n">
-        <v>2.44027256965637</v>
+        <v>2.31940960884094</v>
       </c>
       <c r="H36" t="n">
-        <v>2.24981498718261</v>
+        <v>2.25316262245178</v>
       </c>
       <c r="I36" t="n">
-        <v>487.272961725697</v>
+        <v>487.697696604806</v>
       </c>
       <c r="J36" t="n">
-        <v>473.3503075301</v>
+        <v>488.045751856156</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>554851.549757916</v>
+        <v>585380.6614544868</v>
       </c>
       <c r="B37" t="n">
-        <v>555446.3812311096</v>
+        <v>581785.4980474056</v>
       </c>
       <c r="C37" t="n">
-        <v>555461.4058127423</v>
+        <v>581820.5234046167</v>
       </c>
       <c r="D37" t="n">
-        <v>559021.5438626123</v>
+        <v>589530.6547836228</v>
       </c>
       <c r="E37" t="n">
-        <v>2.2495858669281</v>
+        <v>2.25304794311523</v>
       </c>
       <c r="F37" t="n">
-        <v>2.51103782653808</v>
+        <v>2.32700586318969</v>
       </c>
       <c r="G37" t="n">
-        <v>2.47818446159362</v>
+        <v>2.3226351737976</v>
       </c>
       <c r="H37" t="n">
-        <v>2.24991035461425</v>
+        <v>2.25591087341308</v>
       </c>
       <c r="I37" t="n">
-        <v>500.963737446258</v>
+        <v>501.409442714546</v>
       </c>
       <c r="J37" t="n">
-        <v>487.272961725697</v>
+        <v>501.989910234195</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>559041.5446381728</v>
+        <v>589570.6563347436</v>
       </c>
       <c r="B38" t="n">
-        <v>559656.3526869492</v>
+        <v>585975.4929276552</v>
       </c>
       <c r="C38" t="n">
-        <v>559671.4014685669</v>
+        <v>586010.5182848736</v>
       </c>
       <c r="D38" t="n">
-        <v>563231.5395184368</v>
+        <v>593760.651215004</v>
       </c>
       <c r="E38" t="n">
-        <v>2.24981498718261</v>
+        <v>2.25549101829528</v>
       </c>
       <c r="F38" t="n">
-        <v>2.5156192779541</v>
+        <v>2.32775020599365</v>
       </c>
       <c r="G38" t="n">
-        <v>2.44380402565002</v>
+        <v>2.32767009735107</v>
       </c>
       <c r="H38" t="n">
-        <v>2.25012040138244</v>
+        <v>2.25785756111145</v>
       </c>
       <c r="I38" t="n">
-        <v>515.117293489247</v>
+        <v>515.121216549407</v>
       </c>
       <c r="J38" t="n">
-        <v>501.1952084377</v>
+        <v>515.93409729962</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>563251.5402939972</v>
+        <v>593800.6527661248</v>
       </c>
       <c r="B39" t="n">
-        <v>563846.3717671799</v>
+        <v>590205.4651590768</v>
       </c>
       <c r="C39" t="n">
-        <v>563861.3963488272</v>
+        <v>590240.5147162549</v>
       </c>
       <c r="D39" t="n">
-        <v>567421.5343987008</v>
+        <v>597950.6460952644</v>
       </c>
       <c r="E39" t="n">
-        <v>2.25021600723266</v>
+        <v>2.25764775276184</v>
       </c>
       <c r="F39" t="n">
-        <v>2.51628756523132</v>
+        <v>2.33028864860534</v>
       </c>
       <c r="G39" t="n">
-        <v>2.48213601112365</v>
+        <v>2.32253980636596</v>
       </c>
       <c r="H39" t="n">
-        <v>2.25027322769165</v>
+        <v>2.25976634025573</v>
       </c>
       <c r="I39" t="n">
-        <v>528.8077797342301</v>
+        <v>529.762617099383</v>
       </c>
       <c r="J39" t="n">
-        <v>515.117293489247</v>
+        <v>529.878259629695</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>567441.5351742612</v>
+        <v>597990.6476463852</v>
       </c>
       <c r="B40" t="n">
-        <v>568056.3432230304</v>
+        <v>594395.4842392933</v>
       </c>
       <c r="C40" t="n">
-        <v>568071.392004648</v>
+        <v>594430.5095965152</v>
       </c>
       <c r="D40" t="n">
-        <v>571631.5300545179</v>
+        <v>602140.6409755212</v>
       </c>
       <c r="E40" t="n">
-        <v>2.25023508071899</v>
+        <v>2.2593080997467</v>
       </c>
       <c r="F40" t="n">
-        <v>2.52062082290649</v>
+        <v>2.33023142814636</v>
       </c>
       <c r="G40" t="n">
-        <v>2.44724011421203</v>
+        <v>2.32427644729614</v>
       </c>
       <c r="H40" t="n">
-        <v>2.25054049491882</v>
+        <v>2.26230478286743</v>
       </c>
       <c r="I40" t="n">
-        <v>542.9616392205349</v>
+        <v>543.474290267729</v>
       </c>
       <c r="J40" t="n">
-        <v>529.039252630758</v>
+        <v>543.822342184553</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>571651.5308300784</v>
+        <v>602180.642526642</v>
       </c>
       <c r="B41" t="n">
-        <v>572246.3623032469</v>
+        <v>598585.4791195536</v>
       </c>
       <c r="C41" t="n">
-        <v>572261.3868849084</v>
+        <v>598620.5044767648</v>
       </c>
       <c r="D41" t="n">
-        <v>575821.5249347785</v>
+        <v>606330.6358557816</v>
       </c>
       <c r="E41" t="n">
-        <v>2.25067400932312</v>
+        <v>2.26213288307189</v>
       </c>
       <c r="F41" t="n">
-        <v>2.52071619033813</v>
+        <v>2.33122372627258</v>
       </c>
       <c r="G41" t="n">
-        <v>2.48597311973571</v>
+        <v>2.32744479179382</v>
       </c>
       <c r="H41" t="n">
-        <v>2.25078868865966</v>
+        <v>2.26448059082031</v>
       </c>
       <c r="I41" t="n">
-        <v>556.65236173343</v>
+        <v>557.186041358523</v>
       </c>
       <c r="J41" t="n">
-        <v>542.9616392205349</v>
+        <v>557.76650689722</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>575841.5257103388</v>
+        <v>606370.6374069025</v>
       </c>
       <c r="B42" t="n">
-        <v>576456.333759108</v>
+        <v>602775.4739998104</v>
       </c>
       <c r="C42" t="n">
-        <v>576471.3825407256</v>
+        <v>602810.4993570144</v>
       </c>
       <c r="D42" t="n">
-        <v>580031.5205905992</v>
+        <v>610560.6322871592</v>
       </c>
       <c r="E42" t="n">
-        <v>2.25080776214599</v>
+        <v>2.26419425010681</v>
       </c>
       <c r="F42" t="n">
-        <v>2.52480149269104</v>
+        <v>2.33152914047241</v>
       </c>
       <c r="G42" t="n">
-        <v>2.45021820068359</v>
+        <v>2.33127737045288</v>
       </c>
       <c r="H42" t="n">
-        <v>2.25099849700927</v>
+        <v>2.26701879501342</v>
       </c>
       <c r="I42" t="n">
-        <v>570.805837176617</v>
+        <v>570.89772952334</v>
       </c>
       <c r="J42" t="n">
-        <v>556.883824632382</v>
+        <v>571.710608342157</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>580051.5213661595</v>
+        <v>610600.6338382836</v>
       </c>
       <c r="B43" t="n">
-        <v>580646.352839328</v>
+        <v>607005.446231232</v>
       </c>
       <c r="C43" t="n">
-        <v>580661.3774209751</v>
+        <v>607040.495788392</v>
       </c>
       <c r="D43" t="n">
-        <v>584221.515470856</v>
+        <v>614750.6271674088</v>
       </c>
       <c r="E43" t="n">
-        <v>2.25094127655029</v>
+        <v>2.26677083969116</v>
       </c>
       <c r="F43" t="n">
-        <v>2.52483963966369</v>
+        <v>2.33425855636596</v>
       </c>
       <c r="G43" t="n">
-        <v>2.48921847343444</v>
+        <v>2.32733035087585</v>
       </c>
       <c r="H43" t="n">
-        <v>2.25111317634582</v>
+        <v>2.26971006393432</v>
       </c>
       <c r="I43" t="n">
-        <v>584.496445892461</v>
+        <v>585.539185583399</v>
       </c>
       <c r="J43" t="n">
-        <v>570.805837176617</v>
+        <v>585.654829238297</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>584241.5162464164</v>
+        <v>614790.6287185332</v>
       </c>
       <c r="B44" t="n">
-        <v>584856.3242951892</v>
+        <v>611195.4653114519</v>
       </c>
       <c r="C44" t="n">
-        <v>584871.3730767887</v>
+        <v>611230.4906686416</v>
       </c>
       <c r="D44" t="n">
-        <v>588431.5111266768</v>
+        <v>618940.6220476656</v>
       </c>
       <c r="E44" t="n">
-        <v>2.25113224983215</v>
+        <v>2.26951909065246</v>
       </c>
       <c r="F44" t="n">
-        <v>2.52842855453491</v>
+        <v>2.3353271484375</v>
       </c>
       <c r="G44" t="n">
-        <v>2.45300531387329</v>
+        <v>2.33011674880981</v>
       </c>
       <c r="H44" t="n">
-        <v>2.25113224983215</v>
+        <v>2.2718858718872</v>
       </c>
       <c r="I44" t="n">
-        <v>598.649872991097</v>
+        <v>599.25093965338</v>
       </c>
       <c r="J44" t="n">
-        <v>584.727909673508</v>
+        <v>599.598994500896</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>588451.5119022372</v>
+        <v>618980.6235987863</v>
       </c>
       <c r="B45" t="n">
-        <v>589046.3433754056</v>
+        <v>615385.4601917124</v>
       </c>
       <c r="C45" t="n">
-        <v>589061.3679570385</v>
+        <v>615420.4855489056</v>
       </c>
       <c r="D45" t="n">
-        <v>592621.50600693</v>
+        <v>623130.6169279116</v>
       </c>
       <c r="E45" t="n">
-        <v>2.25115132331848</v>
+        <v>2.27167582511901</v>
       </c>
       <c r="F45" t="n">
-        <v>2.52848577499389</v>
+        <v>2.33605241775512</v>
       </c>
       <c r="G45" t="n">
-        <v>2.49236822128295</v>
+        <v>2.33275055885314</v>
       </c>
       <c r="H45" t="n">
-        <v>2.2513039112091</v>
+        <v>2.27427148818969</v>
       </c>
       <c r="I45" t="n">
-        <v>612.340981503687</v>
+        <v>612.962742905434</v>
       </c>
       <c r="J45" t="n">
-        <v>598.649872991097</v>
+        <v>613.543210805281</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>592641.506782494</v>
+        <v>623170.618479036</v>
       </c>
       <c r="B46" t="n">
-        <v>593256.3148312559</v>
+        <v>619575.4550719728</v>
       </c>
       <c r="C46" t="n">
-        <v>593271.3636128557</v>
+        <v>619610.4804291624</v>
       </c>
       <c r="D46" t="n">
-        <v>596831.5016627436</v>
+        <v>627360.6133592929</v>
       </c>
       <c r="E46" t="n">
-        <v>2.25105595588684</v>
+        <v>2.27398514747619</v>
       </c>
       <c r="F46" t="n">
-        <v>2.53039479255676</v>
+        <v>2.33683514595031</v>
       </c>
       <c r="G46" t="n">
-        <v>2.4542269706726</v>
+        <v>2.33640789985656</v>
       </c>
       <c r="H46" t="n">
-        <v>2.25134229660034</v>
+        <v>2.2770390510559</v>
       </c>
       <c r="I46" t="n">
-        <v>626.493729571117</v>
+        <v>626.674500548686</v>
       </c>
       <c r="J46" t="n">
-        <v>612.5724645184559</v>
+        <v>627.487379384405</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>596851.502438304</v>
+        <v>627400.6149104135</v>
       </c>
       <c r="B47" t="n">
-        <v>597446.3339114868</v>
+        <v>623805.4273033657</v>
       </c>
       <c r="C47" t="n">
-        <v>597461.3584931196</v>
+        <v>623840.4768605436</v>
       </c>
       <c r="D47" t="n">
-        <v>601021.4965429967</v>
+        <v>631550.6082395532</v>
       </c>
       <c r="E47" t="n">
-        <v>2.25120854377746</v>
+        <v>2.27673363685607</v>
       </c>
       <c r="F47" t="n">
-        <v>2.53213191032409</v>
+        <v>2.33969783782959</v>
       </c>
       <c r="G47" t="n">
-        <v>2.49542260169982</v>
+        <v>2.33343768119812</v>
       </c>
       <c r="H47" t="n">
-        <v>2.25143766403198</v>
+        <v>2.27953934669494</v>
       </c>
       <c r="I47" t="n">
-        <v>640.184209759975</v>
+        <v>641.3159903132751</v>
       </c>
       <c r="J47" t="n">
-        <v>626.493729571117</v>
+        <v>641.431634174174</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>601041.4973185608</v>
+        <v>631590.6097906739</v>
       </c>
       <c r="B48" t="n">
-        <v>601656.3053673193</v>
+        <v>627995.4463836108</v>
       </c>
       <c r="C48" t="n">
-        <v>601671.3541489368</v>
+        <v>628030.4717408039</v>
       </c>
       <c r="D48" t="n">
-        <v>605231.4921988103</v>
+        <v>635740.60311981</v>
       </c>
       <c r="E48" t="n">
-        <v>2.25141859054565</v>
+        <v>2.27919578552246</v>
       </c>
       <c r="F48" t="n">
-        <v>2.53682804107666</v>
+        <v>2.34061408042907</v>
       </c>
       <c r="G48" t="n">
-        <v>2.45989656448364</v>
+        <v>2.3358998298645</v>
       </c>
       <c r="H48" t="n">
-        <v>2.25149488449096</v>
+        <v>2.28184866905212</v>
       </c>
       <c r="I48" t="n">
-        <v>654.337713725591</v>
+        <v>655.027789629846</v>
       </c>
       <c r="J48" t="n">
-        <v>640.4156865525611</v>
+        <v>655.375843814673</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>605251.4929743708</v>
+        <v>635780.6046709344</v>
       </c>
       <c r="B49" t="n">
-        <v>605846.3244475679</v>
+        <v>632185.4412638604</v>
       </c>
       <c r="C49" t="n">
-        <v>605861.3490291971</v>
+        <v>632220.4666210607</v>
       </c>
       <c r="D49" t="n">
-        <v>609421.4870790672</v>
+        <v>639930.598000074</v>
       </c>
       <c r="E49" t="n">
-        <v>2.2515902519226</v>
+        <v>2.28142881393432</v>
       </c>
       <c r="F49" t="n">
-        <v>2.53799247741699</v>
+        <v>2.3416256904602</v>
       </c>
       <c r="G49" t="n">
-        <v>2.50059580802917</v>
+        <v>2.3385145664215</v>
       </c>
       <c r="H49" t="n">
-        <v>2.25166678428649</v>
+        <v>2.28503584861755</v>
       </c>
       <c r="I49" t="n">
-        <v>668.027956975826</v>
+        <v>668.7395992294799</v>
       </c>
       <c r="J49" t="n">
-        <v>654.337713725591</v>
+        <v>669.320069833931</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>609441.4878546277</v>
+        <v>639970.5995511948</v>
       </c>
       <c r="B50" t="n">
-        <v>610056.2959033968</v>
+        <v>636375.4361441171</v>
       </c>
       <c r="C50" t="n">
-        <v>610071.3446850181</v>
+        <v>636410.4615013249</v>
       </c>
       <c r="D50" t="n">
-        <v>613631.482734888</v>
+        <v>644160.5944314552</v>
       </c>
       <c r="E50" t="n">
-        <v>2.25155210494995</v>
+        <v>2.28469252586364</v>
       </c>
       <c r="F50" t="n">
-        <v>2.54192495346069</v>
+        <v>2.34227442741394</v>
       </c>
       <c r="G50" t="n">
-        <v>2.46396279335022</v>
+        <v>2.34242033958435</v>
       </c>
       <c r="H50" t="n">
-        <v>2.25172400474548</v>
+        <v>2.28854775428772</v>
       </c>
       <c r="I50" t="n">
-        <v>682.181163319059</v>
+        <v>682.451422467414</v>
       </c>
       <c r="J50" t="n">
-        <v>668.259423771931</v>
+        <v>683.2643040331531</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>613651.4835104484</v>
+        <v>644200.595982576</v>
       </c>
       <c r="B51" t="n">
-        <v>614246.3149836384</v>
+        <v>640605.4083755243</v>
       </c>
       <c r="C51" t="n">
-        <v>614261.3395652784</v>
+        <v>640640.457932706</v>
       </c>
       <c r="D51" t="n">
-        <v>617821.4776151484</v>
+        <v>648350.589311712</v>
       </c>
       <c r="E51" t="n">
-        <v>2.25160956382751</v>
+        <v>2.2883186340332</v>
       </c>
       <c r="F51" t="n">
-        <v>2.54282212257385</v>
+        <v>2.34586262702941</v>
       </c>
       <c r="G51" t="n">
-        <v>2.50492906570434</v>
+        <v>2.34011793136596</v>
       </c>
       <c r="H51" t="n">
-        <v>2.2518765926361</v>
+        <v>2.29215502738952</v>
       </c>
       <c r="I51" t="n">
-        <v>695.871612199016</v>
+        <v>697.092910174127</v>
       </c>
       <c r="J51" t="n">
-        <v>682.181163319059</v>
+        <v>697.208555007106</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>617841.4783907124</v>
+        <v>648390.5908628363</v>
       </c>
       <c r="B52" t="n">
-        <v>618456.2864394853</v>
+        <v>644795.4274557444</v>
       </c>
       <c r="C52" t="n">
-        <v>618471.3352211028</v>
+        <v>644830.4528129628</v>
       </c>
       <c r="D52" t="n">
-        <v>622031.4732709727</v>
+        <v>652540.5841919724</v>
       </c>
       <c r="E52" t="n">
-        <v>2.25172400474548</v>
+        <v>2.29184961318969</v>
       </c>
       <c r="F52" t="n">
-        <v>2.54700279235839</v>
+        <v>2.34754228591918</v>
       </c>
       <c r="G52" t="n">
-        <v>2.46812438964843</v>
+        <v>2.34353423118591</v>
       </c>
       <c r="H52" t="n">
-        <v>2.2518765926361</v>
+        <v>2.29547595977783</v>
       </c>
       <c r="I52" t="n">
-        <v>710.025445366841</v>
+        <v>710.804747745558</v>
       </c>
       <c r="J52" t="n">
-        <v>696.103094878005</v>
+        <v>711.152805008596</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>622051.4740465332</v>
+        <v>652580.5857430932</v>
       </c>
       <c r="B53" t="n">
-        <v>622646.3055197052</v>
+        <v>648985.4223360048</v>
       </c>
       <c r="C53" t="n">
-        <v>622661.3301013631</v>
+        <v>649020.4476932231</v>
       </c>
       <c r="D53" t="n">
-        <v>626221.4681512332</v>
+        <v>656730.5790722328</v>
       </c>
       <c r="E53" t="n">
-        <v>2.25181937217712</v>
+        <v>2.29524683952331</v>
       </c>
       <c r="F53" t="n">
-        <v>2.54887342453002</v>
+        <v>2.34905004501342</v>
       </c>
       <c r="G53" t="n">
-        <v>2.51008343696594</v>
+        <v>2.34624433517456</v>
       </c>
       <c r="H53" t="n">
-        <v>2.25218224525451</v>
+        <v>2.29894948005676</v>
       </c>
       <c r="I53" t="n">
-        <v>723.716917475433</v>
+        <v>724.5166268480669</v>
       </c>
       <c r="J53" t="n">
-        <v>710.025445366841</v>
+        <v>725.097096208325</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>626241.4689267937</v>
+        <v>656770.5806233536</v>
       </c>
       <c r="B54" t="n">
-        <v>626856.2769755628</v>
+        <v>653175.4172162616</v>
       </c>
       <c r="C54" t="n">
-        <v>626871.3257571805</v>
+        <v>653210.4425734765</v>
       </c>
       <c r="D54" t="n">
-        <v>630431.463807054</v>
+        <v>660960.5755036104</v>
       </c>
       <c r="E54" t="n">
-        <v>2.25204849243164</v>
+        <v>2.29870152473449</v>
       </c>
       <c r="F54" t="n">
-        <v>2.55339789390564</v>
+        <v>2.35048151016235</v>
       </c>
       <c r="G54" t="n">
-        <v>2.47329759597778</v>
+        <v>2.35107803344726</v>
       </c>
       <c r="H54" t="n">
-        <v>2.2521629333496</v>
+        <v>2.30232787132263</v>
       </c>
       <c r="I54" t="n">
-        <v>737.8705755740619</v>
+        <v>738.228675812299</v>
       </c>
       <c r="J54" t="n">
-        <v>723.9483879282</v>
+        <v>739.04157151687</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>630451.4645826144</v>
+        <v>661000.5770547348</v>
       </c>
       <c r="B55" t="n">
-        <v>631046.2960557792</v>
+        <v>657405.3894476832</v>
       </c>
       <c r="C55" t="n">
-        <v>631061.3206374409</v>
+        <v>657440.4390048503</v>
       </c>
       <c r="D55" t="n">
-        <v>634621.4586873108</v>
+        <v>665150.5703838707</v>
       </c>
       <c r="E55" t="n">
-        <v>2.25214385986328</v>
+        <v>2.30213689804077</v>
       </c>
       <c r="F55" t="n">
-        <v>2.55523037910461</v>
+        <v>2.35366868972778</v>
       </c>
       <c r="G55" t="n">
-        <v>2.51556205749511</v>
+        <v>2.34874463081359</v>
       </c>
       <c r="H55" t="n">
-        <v>2.25233483314514</v>
+        <v>2.30568695068359</v>
       </c>
       <c r="I55" t="n">
-        <v>751.561492974356</v>
+        <v>752.8703310449411</v>
       </c>
       <c r="J55" t="n">
-        <v>737.8705755740619</v>
+        <v>752.985976964268</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>634641.4594628712</v>
+        <v>665190.5719349916</v>
       </c>
       <c r="B56" t="n">
-        <v>635256.2675116403</v>
+        <v>661595.4085279031</v>
       </c>
       <c r="C56" t="n">
-        <v>635271.3162932508</v>
+        <v>661630.4338851001</v>
       </c>
       <c r="D56" t="n">
-        <v>638831.4543431316</v>
+        <v>669340.5652641205</v>
       </c>
       <c r="E56" t="n">
-        <v>2.25227761268615</v>
+        <v>2.30545783042907</v>
       </c>
       <c r="F56" t="n">
-        <v>2.55939197540283</v>
+        <v>2.35523390769958</v>
       </c>
       <c r="G56" t="n">
-        <v>2.47843265533447</v>
+        <v>2.35147380828857</v>
       </c>
       <c r="H56" t="n">
-        <v>2.25243020057678</v>
+        <v>2.30954217910766</v>
       </c>
       <c r="I56" t="n">
-        <v>765.714655451803</v>
+        <v>766.582218128417</v>
       </c>
       <c r="J56" t="n">
-        <v>751.7929797639219</v>
+        <v>766.930275697011</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>638851.455118692</v>
+        <v>669380.5668152447</v>
       </c>
       <c r="B57" t="n">
-        <v>639446.2865918605</v>
+        <v>665785.40340816</v>
       </c>
       <c r="C57" t="n">
-        <v>639461.311173504</v>
+        <v>665820.4287653496</v>
       </c>
       <c r="D57" t="n">
-        <v>643021.4492233885</v>
+        <v>673530.5601443736</v>
       </c>
       <c r="E57" t="n">
-        <v>2.25231575965881</v>
+        <v>2.3092176914215</v>
       </c>
       <c r="F57" t="n">
-        <v>2.5617971420288</v>
+        <v>2.35624527931213</v>
       </c>
       <c r="G57" t="n">
-        <v>2.52138447761535</v>
+        <v>2.35385966300964</v>
       </c>
       <c r="H57" t="n">
-        <v>2.25258302688598</v>
+        <v>2.31435179710388</v>
       </c>
       <c r="I57" t="n">
-        <v>779.4051500484831</v>
+        <v>780.294129064742</v>
       </c>
       <c r="J57" t="n">
-        <v>765.714655451803</v>
+        <v>780.8746026322769</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>643041.4499989523</v>
+        <v>673570.5616954979</v>
       </c>
       <c r="B58" t="n">
-        <v>643656.2580477216</v>
+        <v>669975.398288424</v>
       </c>
       <c r="C58" t="n">
-        <v>643671.306829314</v>
+        <v>670010.4236456136</v>
       </c>
       <c r="D58" t="n">
-        <v>647231.4448792092</v>
+        <v>677760.5565757512</v>
       </c>
       <c r="E58" t="n">
-        <v>2.25264024734497</v>
+        <v>2.31395101547241</v>
       </c>
       <c r="F58" t="n">
-        <v>2.56599688529968</v>
+        <v>2.3582112789154</v>
       </c>
       <c r="G58" t="n">
-        <v>2.48377776145935</v>
+        <v>2.35821270942688</v>
       </c>
       <c r="H58" t="n">
-        <v>2.25271654129028</v>
+        <v>2.31826448440551</v>
       </c>
       <c r="I58" t="n">
-        <v>793.559203197566</v>
+        <v>794.006047757889</v>
       </c>
       <c r="J58" t="n">
-        <v>779.636635937169</v>
+        <v>794.81893668793</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>647251.4456547697</v>
+        <v>677800.5581268757</v>
       </c>
       <c r="B59" t="n">
-        <v>647846.277127938</v>
+        <v>674205.3705198276</v>
       </c>
       <c r="C59" t="n">
-        <v>647861.3017095672</v>
+        <v>674240.4200769984</v>
       </c>
       <c r="D59" t="n">
-        <v>651421.4397594589</v>
+        <v>681950.551456008</v>
       </c>
       <c r="E59" t="n">
-        <v>2.25279307365417</v>
+        <v>2.31792092323303</v>
       </c>
       <c r="F59" t="n">
-        <v>2.56872677803039</v>
+        <v>2.36178016662597</v>
       </c>
       <c r="G59" t="n">
-        <v>2.52743577957153</v>
+        <v>2.35767674446106</v>
       </c>
       <c r="H59" t="n">
-        <v>2.2528121471405</v>
+        <v>2.32345581054687</v>
       </c>
       <c r="I59" t="n">
-        <v>807.250376217171</v>
+        <v>808.647631550033</v>
       </c>
       <c r="J59" t="n">
-        <v>793.559203197566</v>
+        <v>808.763275901871</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>651441.4405350192</v>
+        <v>681990.5530071288</v>
       </c>
       <c r="B60" t="n">
-        <v>652056.2485837848</v>
+        <v>678395.3896000657</v>
       </c>
       <c r="C60" t="n">
-        <v>652071.2973653916</v>
+        <v>678430.4149572587</v>
       </c>
       <c r="D60" t="n">
-        <v>655631.4354152724</v>
+        <v>686140.5463362648</v>
       </c>
       <c r="E60" t="n">
-        <v>2.25286936759948</v>
+        <v>2.32307410240173</v>
       </c>
       <c r="F60" t="n">
-        <v>2.57336544990539</v>
+        <v>2.36313533782959</v>
       </c>
       <c r="G60" t="n">
-        <v>2.48990559577941</v>
+        <v>2.35981440544128</v>
       </c>
       <c r="H60" t="n">
-        <v>2.25298380851745</v>
+        <v>2.32914352416992</v>
       </c>
       <c r="I60" t="n">
-        <v>821.404604975185</v>
+        <v>822.359492563196</v>
       </c>
       <c r="J60" t="n">
-        <v>807.481865651434</v>
+        <v>822.707550140426</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>655651.4361908364</v>
+        <v>686180.5478873856</v>
       </c>
       <c r="B61" t="n">
-        <v>656246.2676640227</v>
+        <v>682585.384480326</v>
       </c>
       <c r="C61" t="n">
-        <v>656261.2922456519</v>
+        <v>682620.4098375156</v>
       </c>
       <c r="D61" t="n">
-        <v>659821.430295522</v>
+        <v>690330.5412165252</v>
       </c>
       <c r="E61" t="n">
-        <v>2.25306034088134</v>
+        <v>2.3289144039154</v>
       </c>
       <c r="F61" t="n">
-        <v>2.57599997520446</v>
+        <v>2.3656165599823</v>
       </c>
       <c r="G61" t="n">
-        <v>2.53379273414611</v>
+        <v>2.36315441131591</v>
       </c>
       <c r="H61" t="n">
-        <v>2.25330853462219</v>
+        <v>2.33498382568359</v>
       </c>
       <c r="I61" t="n">
-        <v>835.095389943521</v>
+        <v>836.071407826193</v>
       </c>
       <c r="J61" t="n">
-        <v>821.404604975185</v>
+        <v>836.651879226766</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>659841.431071086</v>
+        <v>690370.542767646</v>
       </c>
       <c r="B62" t="n">
-        <v>660456.2391198516</v>
+        <v>686775.3793605756</v>
       </c>
       <c r="C62" t="n">
-        <v>660471.2879014692</v>
+        <v>686810.404717776</v>
       </c>
       <c r="D62" t="n">
-        <v>664031.4259513428</v>
+        <v>694560.53764791</v>
       </c>
       <c r="E62" t="n">
-        <v>2.253098487854</v>
+        <v>2.33467841148376</v>
       </c>
       <c r="F62" t="n">
-        <v>2.58004689216613</v>
+        <v>2.36805963516235</v>
       </c>
       <c r="G62" t="n">
-        <v>2.49557518959045</v>
+        <v>2.36807298660278</v>
       </c>
       <c r="H62" t="n">
-        <v>2.25319385528564</v>
+        <v>2.34004139900207</v>
       </c>
       <c r="I62" t="n">
-        <v>849.248502697951</v>
+        <v>849.783308779985</v>
       </c>
       <c r="J62" t="n">
-        <v>835.326873778521</v>
+        <v>850.596199557021</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>664051.4267269032</v>
+        <v>694600.5391990308</v>
       </c>
       <c r="B63" t="n">
-        <v>664646.2582001004</v>
+        <v>691005.3515919792</v>
       </c>
       <c r="C63" t="n">
-        <v>664661.2827817296</v>
+        <v>691040.4011491608</v>
       </c>
       <c r="D63" t="n">
-        <v>668221.4208315995</v>
+        <v>698750.5325281705</v>
       </c>
       <c r="E63" t="n">
-        <v>2.25319385528564</v>
+        <v>2.34002232551574</v>
       </c>
       <c r="F63" t="n">
-        <v>2.58285307884216</v>
+        <v>2.37174320220947</v>
       </c>
       <c r="G63" t="n">
-        <v>2.53993964195251</v>
+        <v>2.36817407608032</v>
       </c>
       <c r="H63" t="n">
-        <v>2.25342297554016</v>
+        <v>2.34601545333862</v>
       </c>
       <c r="I63" t="n">
-        <v>862.939014469887</v>
+        <v>864.424867526433</v>
       </c>
       <c r="J63" t="n">
-        <v>849.248502697951</v>
+        <v>864.540512328017</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>668241.42160716</v>
+        <v>698790.5340792948</v>
       </c>
       <c r="B64" t="n">
-        <v>668856.2296559328</v>
+        <v>695195.37067221</v>
       </c>
       <c r="C64" t="n">
-        <v>668871.2784375504</v>
+        <v>695230.3960294211</v>
       </c>
       <c r="D64" t="n">
-        <v>672431.4164874204</v>
+        <v>702940.5274084308</v>
       </c>
       <c r="E64" t="n">
-        <v>2.25330853462219</v>
+        <v>2.34597706794738</v>
       </c>
       <c r="F64" t="n">
-        <v>2.58699560165405</v>
+        <v>2.37368988990783</v>
       </c>
       <c r="G64" t="n">
-        <v>2.50162672996521</v>
+        <v>2.370769739151</v>
       </c>
       <c r="H64" t="n">
-        <v>2.2532320022583</v>
+        <v>2.35242819786071</v>
       </c>
       <c r="I64" t="n">
-        <v>877.092847332724</v>
+        <v>878.136738102657</v>
       </c>
       <c r="J64" t="n">
-        <v>863.170485794119</v>
+        <v>878.484797789078</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>672451.4172629808</v>
+        <v>702980.5289595516</v>
       </c>
       <c r="B65" t="n">
-        <v>673046.2487361636</v>
+        <v>699385.3655524596</v>
       </c>
       <c r="C65" t="n">
-        <v>673061.2733178108</v>
+        <v>699420.3909096816</v>
       </c>
       <c r="D65" t="n">
-        <v>676621.4113676844</v>
+        <v>707130.5222886913</v>
       </c>
       <c r="E65" t="n">
-        <v>2.25340390205383</v>
+        <v>2.35214185714721</v>
       </c>
       <c r="F65" t="n">
-        <v>2.58943915367126</v>
+        <v>2.3762092590332</v>
       </c>
       <c r="G65" t="n">
-        <v>2.54604816436767</v>
+        <v>2.3740906715393</v>
       </c>
       <c r="H65" t="n">
-        <v>2.25334668159484</v>
+        <v>2.35844016075134</v>
       </c>
       <c r="I65" t="n">
-        <v>890.783427067217</v>
+        <v>891.848608419602</v>
       </c>
       <c r="J65" t="n">
-        <v>877.092847332724</v>
+        <v>892.429081188752</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>676641.4121432448</v>
+        <v>707170.523839812</v>
       </c>
       <c r="B66" t="n">
-        <v>677256.220192014</v>
+        <v>703575.3604327199</v>
       </c>
       <c r="C66" t="n">
-        <v>677271.2689736316</v>
+        <v>703610.385789942</v>
       </c>
       <c r="D66" t="n">
-        <v>680831.4070235016</v>
+        <v>711360.5187200687</v>
       </c>
       <c r="E66" t="n">
-        <v>2.2535183429718</v>
+        <v>2.35823035240173</v>
       </c>
       <c r="F66" t="n">
-        <v>2.59340977668762</v>
+        <v>2.37911033630371</v>
       </c>
       <c r="G66" t="n">
-        <v>2.50727725028991</v>
+        <v>2.37897539138793</v>
       </c>
       <c r="H66" t="n">
-        <v>2.25344204902648</v>
+        <v>2.36445236206054</v>
       </c>
       <c r="I66" t="n">
-        <v>904.936208523963</v>
+        <v>905.560505792899</v>
       </c>
       <c r="J66" t="n">
-        <v>891.0148919523421</v>
+        <v>906.373391381999</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>680851.4077990621</v>
+        <v>711400.5202711932</v>
       </c>
       <c r="B67" t="n">
-        <v>681446.2392722304</v>
+        <v>707805.3326641415</v>
       </c>
       <c r="C67" t="n">
-        <v>681461.263853892</v>
+        <v>707840.3822213196</v>
       </c>
       <c r="D67" t="n">
-        <v>685021.401903762</v>
+        <v>715550.5136003292</v>
       </c>
       <c r="E67" t="n">
-        <v>2.25340390205383</v>
+        <v>2.36429953575134</v>
       </c>
       <c r="F67" t="n">
-        <v>2.59650230407714</v>
+        <v>2.38313746452331</v>
       </c>
       <c r="G67" t="n">
-        <v>2.55244326591491</v>
+        <v>2.37983560562133</v>
       </c>
       <c r="H67" t="n">
-        <v>2.25346112251281</v>
+        <v>2.36991095542907</v>
       </c>
       <c r="I67" t="n">
-        <v>918.6273966822901</v>
+        <v>920.202099451604</v>
       </c>
       <c r="J67" t="n">
-        <v>904.936208523963</v>
+        <v>920.317744860686</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>685041.4026793224</v>
+        <v>715590.5151514501</v>
       </c>
       <c r="B68" t="n">
-        <v>685656.2107280915</v>
+        <v>711995.351744358</v>
       </c>
       <c r="C68" t="n">
-        <v>685671.2595097092</v>
+        <v>712030.3771015692</v>
       </c>
       <c r="D68" t="n">
-        <v>689231.3975595828</v>
+        <v>719740.5084805896</v>
       </c>
       <c r="E68" t="n">
-        <v>2.25346112251281</v>
+        <v>2.36979627609252</v>
       </c>
       <c r="F68" t="n">
-        <v>2.60079741477966</v>
+        <v>2.38638186454772</v>
       </c>
       <c r="G68" t="n">
-        <v>2.51332855224609</v>
+        <v>2.38336634635925</v>
       </c>
       <c r="H68" t="n">
-        <v>2.25359487533569</v>
+        <v>2.37454867362976</v>
       </c>
       <c r="I68" t="n">
-        <v>932.781160605777</v>
+        <v>933.914034385058</v>
       </c>
       <c r="J68" t="n">
-        <v>918.858888944774</v>
+        <v>934.262093676478</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>689251.3983351432</v>
+        <v>719780.5100317104</v>
       </c>
       <c r="B69" t="n">
-        <v>689846.2298083116</v>
+        <v>716185.3466246184</v>
       </c>
       <c r="C69" t="n">
-        <v>689861.2543899624</v>
+        <v>716220.3719818188</v>
       </c>
       <c r="D69" t="n">
-        <v>693421.3924398397</v>
+        <v>723930.5033608356</v>
       </c>
       <c r="E69" t="n">
-        <v>2.25346112251281</v>
+        <v>2.3745105266571</v>
       </c>
       <c r="F69" t="n">
-        <v>2.60423350334167</v>
+        <v>2.38939762115478</v>
       </c>
       <c r="G69" t="n">
-        <v>2.55933475494384</v>
+        <v>2.38697361946106</v>
       </c>
       <c r="H69" t="n">
-        <v>2.25363302230835</v>
+        <v>2.37920570373535</v>
       </c>
       <c r="I69" t="n">
-        <v>946.471953605057</v>
+        <v>947.625970016804</v>
       </c>
       <c r="J69" t="n">
-        <v>932.781160605777</v>
+        <v>948.206447405976</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>693441.3932154001</v>
+        <v>723970.50491196</v>
       </c>
       <c r="B70" t="n">
-        <v>694056.2012641728</v>
+        <v>720375.3415048788</v>
       </c>
       <c r="C70" t="n">
-        <v>694071.250045776</v>
+        <v>720410.3668620684</v>
       </c>
       <c r="D70" t="n">
-        <v>697631.3880956604</v>
+        <v>728160.4997922168</v>
       </c>
       <c r="E70" t="n">
-        <v>2.25349926948547</v>
+        <v>2.37912940979003</v>
       </c>
       <c r="F70" t="n">
-        <v>2.60883402824401</v>
+        <v>2.39226055145263</v>
       </c>
       <c r="G70" t="n">
-        <v>2.51966643333435</v>
+        <v>2.39132070541381</v>
       </c>
       <c r="H70" t="n">
-        <v>2.25361394882202</v>
+        <v>2.3834044933319</v>
       </c>
       <c r="I70" t="n">
-        <v>960.625039426566</v>
+        <v>961.337843656153</v>
       </c>
       <c r="J70" t="n">
-        <v>946.703443967447</v>
+        <v>962.150727478007</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>697651.3888712208</v>
+        <v>728200.5013433412</v>
       </c>
       <c r="B71" t="n">
-        <v>698246.2203443892</v>
+        <v>724605.3137362896</v>
       </c>
       <c r="C71" t="n">
-        <v>698261.2449260256</v>
+        <v>724640.3632934532</v>
       </c>
       <c r="D71" t="n">
-        <v>701821.3829759208</v>
+        <v>732350.49467247</v>
       </c>
       <c r="E71" t="n">
-        <v>2.25355648994445</v>
+        <v>2.38321375846862</v>
       </c>
       <c r="F71" t="n">
-        <v>2.61311030387878</v>
+        <v>2.39584851264953</v>
       </c>
       <c r="G71" t="n">
-        <v>2.56719970703125</v>
+        <v>2.39260387420654</v>
       </c>
       <c r="H71" t="n">
-        <v>2.25388121604919</v>
+        <v>2.38724088668823</v>
       </c>
       <c r="I71" t="n">
-        <v>974.316255625532</v>
+        <v>975.979423213704</v>
       </c>
       <c r="J71" t="n">
-        <v>960.625039426566</v>
+        <v>976.095067132328</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>701841.3837514812</v>
+        <v>732390.4962235944</v>
       </c>
       <c r="B72" t="n">
-        <v>702456.1918002432</v>
+        <v>728795.332816524</v>
       </c>
       <c r="C72" t="n">
-        <v>702471.2405818392</v>
+        <v>728830.3581737136</v>
       </c>
       <c r="D72" t="n">
-        <v>706031.3786317308</v>
+        <v>736540.4895527232</v>
       </c>
       <c r="E72" t="n">
-        <v>2.25388121604919</v>
+        <v>2.38733625411987</v>
       </c>
       <c r="F72" t="n">
-        <v>2.61874175071716</v>
+        <v>2.39871144294738</v>
       </c>
       <c r="G72" t="n">
-        <v>2.5275695323944</v>
+        <v>2.39584851264953</v>
       </c>
       <c r="H72" t="n">
-        <v>2.25407195091247</v>
+        <v>2.39098167419433</v>
       </c>
       <c r="I72" t="n">
-        <v>988.469076682482</v>
+        <v>989.691336362196</v>
       </c>
       <c r="J72" t="n">
-        <v>974.5477344682701</v>
+        <v>990.039393942372</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>706051.3794072912</v>
+        <v>736580.491103844</v>
       </c>
       <c r="B73" t="n">
-        <v>706646.2108804705</v>
+        <v>732985.3276967844</v>
       </c>
       <c r="C73" t="n">
-        <v>706661.2354620997</v>
+        <v>733020.353053974</v>
       </c>
       <c r="D73" t="n">
-        <v>710221.3735119839</v>
+        <v>740730.4844329837</v>
       </c>
       <c r="E73" t="n">
-        <v>2.25412917137146</v>
+        <v>2.39103889465332</v>
       </c>
       <c r="F73" t="n">
-        <v>2.62427759170532</v>
+        <v>2.40180325508117</v>
       </c>
       <c r="G73" t="n">
-        <v>2.57710719108581</v>
+        <v>2.3993604183197</v>
       </c>
       <c r="H73" t="n">
-        <v>2.25451111793518</v>
+        <v>2.39460802078247</v>
       </c>
       <c r="I73" t="n">
-        <v>1002.1590998056</v>
+        <v>1003.40324347712</v>
       </c>
       <c r="J73" t="n">
-        <v>988.469076682482</v>
+        <v>1003.98371809137</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>710241.374287548</v>
+        <v>740770.4859841043</v>
       </c>
       <c r="B74" t="n">
-        <v>710856.1823363135</v>
+        <v>737175.3225770412</v>
       </c>
       <c r="C74" t="n">
-        <v>710871.231117924</v>
+        <v>737210.3479342344</v>
       </c>
       <c r="D74" t="n">
-        <v>714431.3691678012</v>
+        <v>744960.4808643648</v>
       </c>
       <c r="E74" t="n">
-        <v>2.2545301914215</v>
+        <v>2.39468431472778</v>
       </c>
       <c r="F74" t="n">
-        <v>2.6312072277069</v>
+        <v>2.40485715866088</v>
       </c>
       <c r="G74" t="n">
-        <v>2.53738164901733</v>
+        <v>2.4042272567749</v>
       </c>
       <c r="H74" t="n">
-        <v>2.25491189956665</v>
+        <v>2.39783358573913</v>
       </c>
       <c r="I74" t="n">
-        <v>1016.31213354222</v>
+        <v>1017.11515798591</v>
       </c>
       <c r="J74" t="n">
-        <v>1002.39055921753</v>
+        <v>1017.92804270058</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>714451.3699433616</v>
+        <v>745000.4824154855</v>
       </c>
       <c r="B75" t="n">
-        <v>715046.2014165552</v>
+        <v>741405.294808434</v>
       </c>
       <c r="C75" t="n">
-        <v>715061.2259981844</v>
+        <v>741440.344365612</v>
       </c>
       <c r="D75" t="n">
-        <v>718621.3640480543</v>
+        <v>749150.4757446252</v>
       </c>
       <c r="E75" t="n">
-        <v>2.25485467910766</v>
+        <v>2.39789080619812</v>
       </c>
       <c r="F75" t="n">
-        <v>2.63794589042663</v>
+        <v>2.40890336036682</v>
       </c>
       <c r="G75" t="n">
-        <v>2.58955359458923</v>
+        <v>2.40541052818298</v>
       </c>
       <c r="H75" t="n">
-        <v>2.25540828704834</v>
+        <v>2.40117359161377</v>
       </c>
       <c r="I75" t="n">
-        <v>1030.00280950821</v>
+        <v>1031.75672919856</v>
       </c>
       <c r="J75" t="n">
-        <v>1016.31213354222</v>
+        <v>1031.87237265077</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>718641.3648236148</v>
+        <v>749190.477295746</v>
       </c>
       <c r="B76" t="n">
-        <v>719256.172872384</v>
+        <v>745595.313888672</v>
       </c>
       <c r="C76" t="n">
-        <v>719271.2216540052</v>
+        <v>745630.3392458759</v>
       </c>
       <c r="D76" t="n">
-        <v>722831.3597038753</v>
+        <v>753340.4706248892</v>
       </c>
       <c r="E76" t="n">
-        <v>2.25537014007568</v>
+        <v>2.40103983879089</v>
       </c>
       <c r="F76" t="n">
-        <v>2.64628791809082</v>
+        <v>2.41230058670043</v>
       </c>
       <c r="G76" t="n">
-        <v>2.5502860546112</v>
+        <v>2.40936136245727</v>
       </c>
       <c r="H76" t="n">
-        <v>2.25596189498901</v>
+        <v>2.40458989143371</v>
       </c>
       <c r="I76" t="n">
-        <v>1044.15641308151</v>
+        <v>1045.46863876127</v>
       </c>
       <c r="J76" t="n">
-        <v>1030.23428425646</v>
+        <v>1045.81669749031</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>722851.3604794357</v>
+        <v>753380.47217601</v>
       </c>
       <c r="B77" t="n">
-        <v>723446.1919526255</v>
+        <v>749785.3087689287</v>
       </c>
       <c r="C77" t="n">
-        <v>723461.2165342621</v>
+        <v>749820.33412614</v>
       </c>
       <c r="D77" t="n">
-        <v>727021.3545841321</v>
+        <v>757530.4655051461</v>
       </c>
       <c r="E77" t="n">
-        <v>2.25603818893432</v>
+        <v>2.40460896492004</v>
       </c>
       <c r="F77" t="n">
-        <v>2.65453481674194</v>
+        <v>2.41627049446106</v>
       </c>
       <c r="G77" t="n">
-        <v>2.6046917438507</v>
+        <v>2.41394209861755</v>
       </c>
       <c r="H77" t="n">
-        <v>2.25670647621154</v>
+        <v>2.40831160545349</v>
       </c>
       <c r="I77" t="n">
-        <v>1057.84668150486</v>
+        <v>1059.18050695642</v>
       </c>
       <c r="J77" t="n">
-        <v>1044.15641308151</v>
+        <v>1059.76098192155</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>727041.355359696</v>
+        <v>757570.4670562703</v>
       </c>
       <c r="B78" t="n">
-        <v>727656.1634084688</v>
+        <v>753975.3036491784</v>
       </c>
       <c r="C78" t="n">
-        <v>727671.2121900864</v>
+        <v>754010.3290063968</v>
       </c>
       <c r="D78" t="n">
-        <v>731231.3502399564</v>
+        <v>761760.4619365272</v>
       </c>
       <c r="E78" t="n">
-        <v>2.25661087036132</v>
+        <v>2.40819716453552</v>
       </c>
       <c r="F78" t="n">
-        <v>2.6642894744873</v>
+        <v>2.42142367362976</v>
       </c>
       <c r="G78" t="n">
-        <v>2.56655049324035</v>
+        <v>2.42130231857299</v>
       </c>
       <c r="H78" t="n">
-        <v>2.25735545158386</v>
+        <v>2.41151809692382</v>
       </c>
       <c r="I78" t="n">
-        <v>1071.99962530536</v>
+        <v>1072.89240794324</v>
       </c>
       <c r="J78" t="n">
-        <v>1058.07815544193</v>
+        <v>1073.70529640869</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>731251.3510155168</v>
+        <v>761800.4634876481</v>
       </c>
       <c r="B79" t="n">
-        <v>731846.182488696</v>
+        <v>758205.2758806</v>
       </c>
       <c r="C79" t="n">
-        <v>731861.2070703504</v>
+        <v>758240.325437778</v>
       </c>
       <c r="D79" t="n">
-        <v>735421.3451202203</v>
+        <v>765950.4568167876</v>
       </c>
       <c r="E79" t="n">
-        <v>2.25746989250183</v>
+        <v>2.41142272949218</v>
       </c>
       <c r="F79" t="n">
-        <v>2.67415881156921</v>
+        <v>2.42978334426879</v>
       </c>
       <c r="G79" t="n">
-        <v>2.62360954284668</v>
+        <v>2.42543172836303</v>
       </c>
       <c r="H79" t="n">
-        <v>2.25838637351989</v>
+        <v>2.41541171073913</v>
       </c>
       <c r="I79" t="n">
-        <v>1085.69019647752</v>
+        <v>1087.53392825229</v>
       </c>
       <c r="J79" t="n">
-        <v>1071.99962530536</v>
+        <v>1087.64957230405</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>735441.3458957808</v>
+        <v>765990.4583679084</v>
       </c>
       <c r="B80" t="n">
-        <v>736056.15394455</v>
+        <v>762395.2949608164</v>
       </c>
       <c r="C80" t="n">
-        <v>736071.2027261676</v>
+        <v>762430.3203180385</v>
       </c>
       <c r="D80" t="n">
-        <v>739631.3407760413</v>
+        <v>770140.4516970444</v>
       </c>
       <c r="E80" t="n">
-        <v>2.25851988792419</v>
+        <v>2.4152398109436</v>
       </c>
       <c r="F80" t="n">
-        <v>2.6867389678955</v>
+        <v>2.44140648841857</v>
       </c>
       <c r="G80" t="n">
-        <v>2.58762550354003</v>
+        <v>2.43766570091247</v>
       </c>
       <c r="H80" t="n">
-        <v>2.25958895683288</v>
+        <v>2.41920971870422</v>
       </c>
       <c r="I80" t="n">
-        <v>1099.84379577065</v>
+        <v>1101.24581081208</v>
       </c>
       <c r="J80" t="n">
-        <v>1085.92165013363</v>
+        <v>1101.59386755225</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>739651.3415516015</v>
+        <v>770180.4532481688</v>
       </c>
       <c r="B81" t="n">
-        <v>740246.17302477</v>
+        <v>766585.2898410768</v>
       </c>
       <c r="C81" t="n">
-        <v>740261.1976064281</v>
+        <v>766620.3151982879</v>
       </c>
       <c r="D81" t="n">
-        <v>743821.3356562981</v>
+        <v>774330.4465773047</v>
       </c>
       <c r="E81" t="n">
-        <v>2.25964617729187</v>
+        <v>2.4189805984497</v>
       </c>
       <c r="F81" t="n">
-        <v>2.70033073425293</v>
+        <v>2.47933030128479</v>
       </c>
       <c r="G81" t="n">
-        <v>2.6489987373352</v>
+        <v>2.48370099067688</v>
       </c>
       <c r="H81" t="n">
-        <v>2.26105880737304</v>
+        <v>2.42539358139038</v>
       </c>
       <c r="I81" t="n">
-        <v>1113.53374774953</v>
+        <v>1114.95763510562</v>
       </c>
       <c r="J81" t="n">
-        <v>1099.84379577065</v>
+        <v>1115.53810881073</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>743841.3364318584</v>
+        <v>774370.4481284256</v>
       </c>
       <c r="B82" t="n">
-        <v>744456.1444806276</v>
+        <v>770775.2847213371</v>
       </c>
       <c r="C82" t="n">
-        <v>744471.1932622417</v>
+        <v>770810.3100785376</v>
       </c>
       <c r="D82" t="n">
-        <v>748031.3313121188</v>
+        <v>778560.4430086788</v>
       </c>
       <c r="E82" t="n">
-        <v>2.26098251342773</v>
+        <v>2.42497372627258</v>
       </c>
       <c r="F82" t="n">
-        <v>2.7178361415863</v>
+        <v>2.59323477745056</v>
       </c>
       <c r="G82" t="n">
-        <v>2.61734819412231</v>
+        <v>2.61490035057067</v>
       </c>
       <c r="H82" t="n">
-        <v>2.26268148422241</v>
+        <v>2.43008875846862</v>
       </c>
       <c r="I82" t="n">
-        <v>1127.68704456291</v>
+        <v>1128.6694434313</v>
       </c>
       <c r="J82" t="n">
-        <v>1113.76522361584</v>
+        <v>1129.48232230235</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>748051.3320876792</v>
+        <v>778600.4445598067</v>
       </c>
       <c r="B83" t="n">
-        <v>748646.1635608475</v>
+        <v>775005.2569527553</v>
       </c>
       <c r="C83" t="n">
-        <v>748661.1881424912</v>
+        <v>775040.3065099115</v>
       </c>
       <c r="D83" t="n">
-        <v>752221.3261923756</v>
+        <v>782750.4378889319</v>
       </c>
       <c r="E83" t="n">
-        <v>2.26275777816772</v>
+        <v>2.42978334426879</v>
       </c>
       <c r="F83" t="n">
-        <v>2.73854827880859</v>
+        <v>2.69782543182373</v>
       </c>
       <c r="G83" t="n">
-        <v>2.68675804138183</v>
+        <v>2.67034173011779</v>
       </c>
       <c r="H83" t="n">
-        <v>2.26499128341674</v>
+        <v>2.43358135223388</v>
       </c>
       <c r="I83" t="n">
-        <v>1141.37769835837</v>
+        <v>1143.31094240651</v>
       </c>
       <c r="J83" t="n">
-        <v>1127.68704456291</v>
+        <v>1143.42658642526</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>752241.3269679396</v>
+        <v>782790.4394400528</v>
       </c>
       <c r="B84" t="n">
-        <v>752856.1350167089</v>
+        <v>779195.2760329752</v>
       </c>
       <c r="C84" t="n">
-        <v>752871.1837983048</v>
+        <v>779230.3013901648</v>
       </c>
       <c r="D84" t="n">
-        <v>756431.3218481963</v>
+        <v>786940.4327691852</v>
       </c>
       <c r="E84" t="n">
-        <v>2.2650294303894</v>
+        <v>2.43333315849304</v>
       </c>
       <c r="F84" t="n">
-        <v>2.76704907417297</v>
+        <v>2.73737120628356</v>
       </c>
       <c r="G84" t="n">
-        <v>2.6642894744873</v>
+        <v>2.71866703033447</v>
       </c>
       <c r="H84" t="n">
-        <v>2.2683892250061</v>
+        <v>2.43703579902648</v>
       </c>
       <c r="I84" t="n">
-        <v>1155.53111274192</v>
+        <v>1157.02279646399</v>
       </c>
       <c r="J84" t="n">
-        <v>1141.60917787359</v>
+        <v>1157.37085255023</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>756451.3226237568</v>
+        <v>786980.4343203097</v>
       </c>
       <c r="B85" t="n">
-        <v>757046.1540969253</v>
+        <v>783385.2709132392</v>
       </c>
       <c r="C85" t="n">
-        <v>757061.1786785545</v>
+        <v>783420.2962704288</v>
       </c>
       <c r="D85" t="n">
-        <v>760621.3167284461</v>
+        <v>791130.4276494385</v>
       </c>
       <c r="E85" t="n">
-        <v>2.26821756362915</v>
+        <v>2.43695950508117</v>
       </c>
       <c r="F85" t="n">
-        <v>2.80312871932983</v>
+        <v>2.76256465911865</v>
       </c>
       <c r="G85" t="n">
-        <v>2.75137662887573</v>
+        <v>2.75397610664367</v>
       </c>
       <c r="H85" t="n">
-        <v>2.27325701713562</v>
+        <v>2.44081497192382</v>
       </c>
       <c r="I85" t="n">
-        <v>1169.22225272179</v>
+        <v>1170.73460276761</v>
       </c>
       <c r="J85" t="n">
-        <v>1155.53111274192</v>
+        <v>1171.31507023907</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>760641.3175040099</v>
+        <v>791170.4292005592</v>
       </c>
       <c r="B86" t="n">
-        <v>761256.1255527756</v>
+        <v>787575.265793496</v>
       </c>
       <c r="C86" t="n">
-        <v>761271.1743343788</v>
+        <v>787610.2911506891</v>
       </c>
       <c r="D86" t="n">
-        <v>764831.3123842633</v>
+        <v>795360.424080816</v>
       </c>
       <c r="E86" t="n">
-        <v>2.27314257621765</v>
+        <v>2.44028043746948</v>
       </c>
       <c r="F86" t="n">
-        <v>2.85759139060974</v>
+        <v>2.78207039833068</v>
       </c>
       <c r="G86" t="n">
-        <v>2.7532091140747</v>
+        <v>2.78877758979797</v>
       </c>
       <c r="H86" t="n">
-        <v>2.28152298927307</v>
+        <v>2.44419312477111</v>
       </c>
       <c r="I86" t="n">
-        <v>1183.3754769465</v>
+        <v>1184.44637146008</v>
       </c>
       <c r="J86" t="n">
-        <v>1169.4537371626</v>
+        <v>1185.25924796691</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>764851.3131598271</v>
+        <v>795400.4256319404</v>
       </c>
       <c r="B87" t="n">
-        <v>765446.1446330136</v>
+        <v>791805.2380248888</v>
       </c>
       <c r="C87" t="n">
-        <v>765461.1692146427</v>
+        <v>791840.2875820668</v>
       </c>
       <c r="D87" t="n">
-        <v>769021.30726452</v>
+        <v>799550.4189610764</v>
       </c>
       <c r="E87" t="n">
-        <v>2.28138923645019</v>
+        <v>2.44377326965332</v>
       </c>
       <c r="F87" t="n">
-        <v>2.94383835792541</v>
+        <v>2.80735921859741</v>
       </c>
       <c r="G87" t="n">
-        <v>2.89399528503418</v>
+        <v>2.77479863166809</v>
       </c>
       <c r="H87" t="n">
-        <v>2.2969856262207</v>
+        <v>2.44860196113586</v>
       </c>
       <c r="I87" t="n">
-        <v>1197.0655187501</v>
+        <v>1199.08786617487</v>
       </c>
       <c r="J87" t="n">
-        <v>1183.3754769465</v>
+        <v>1199.20350956869</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>769041.3080400804</v>
+        <v>799590.4205121972</v>
       </c>
       <c r="B88" t="n">
-        <v>769468.6779178751</v>
+        <v>795995.257105134</v>
       </c>
       <c r="C88" t="n">
-        <v>769483.7268994944</v>
+        <v>796030.2824623273</v>
       </c>
       <c r="D88" t="n">
-        <v>773043.8649493681</v>
+        <v>803740.4138413403</v>
       </c>
       <c r="E88" t="n">
-        <v>2.2966992855072</v>
+        <v>2.44814395904541</v>
       </c>
       <c r="F88" t="n">
-        <v>3.00003838539123</v>
+        <v>2.8223226070404</v>
       </c>
       <c r="G88" t="n">
-        <v>2.89746975898742</v>
+        <v>2.79863691329956</v>
       </c>
       <c r="H88" t="n">
-        <v>2.3160560131073</v>
+        <v>2.45247650146484</v>
       </c>
       <c r="I88" t="n">
-        <v>1206.86998397241</v>
+        <v>1212.7997557333</v>
       </c>
       <c r="J88" t="n">
-        <v>1197.29699003364</v>
+        <v>1213.14781338938</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>773063.8657249283</v>
+        <v>803780.4153924612</v>
       </c>
       <c r="B89" t="n">
-        <v>773290.1330484733</v>
+        <v>800185.2519853872</v>
       </c>
       <c r="C89" t="n">
-        <v>773305.1820300708</v>
+        <v>800220.2773425912</v>
       </c>
       <c r="D89" t="n">
-        <v>776865.320079966</v>
+        <v>807930.4087216008</v>
       </c>
       <c r="E89" t="n">
-        <v>2.31573152542114</v>
+        <v>2.45201826095581</v>
       </c>
       <c r="F89" t="n">
-        <v>2.99988579750061</v>
+        <v>2.83659887313842</v>
       </c>
       <c r="G89" t="n">
-        <v>2.90197491645813</v>
+        <v>2.82400202751159</v>
       </c>
       <c r="H89" t="n">
-        <v>2.33216786384582</v>
+        <v>2.4585838317871</v>
       </c>
       <c r="I89" t="n">
-        <v>1212.00864768579</v>
+        <v>1226.51162491903</v>
       </c>
       <c r="J89" t="n">
-        <v>1206.86998397241</v>
+        <v>1227.09209712175</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>776885.3208555265</v>
+        <v>807970.4102727216</v>
       </c>
       <c r="B90" t="n">
-        <v>777060.1360419192</v>
+        <v>804375.246865644</v>
       </c>
       <c r="C90" t="n">
-        <v>777066.4586341871</v>
+        <v>804410.2722228516</v>
       </c>
       <c r="D90" t="n">
-        <v>780646.5974596213</v>
+        <v>812160.405152982</v>
       </c>
       <c r="E90" t="n">
-        <v>2.33186244964599</v>
+        <v>2.45780134201049</v>
       </c>
       <c r="F90" t="n">
-        <v>2.99627780914306</v>
+        <v>2.84709596633911</v>
       </c>
       <c r="G90" t="n">
-        <v>2.99388718605041</v>
+        <v>2.85130620002746</v>
       </c>
       <c r="H90" t="n">
-        <v>2.34669494628906</v>
+        <v>2.46572208404541</v>
       </c>
       <c r="I90" t="n">
-        <v>1215.95349915548</v>
+        <v>1240.22347860543</v>
       </c>
       <c r="J90" t="n">
-        <v>1212.00864768579</v>
+        <v>1241.03635868952</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>780666.4062354168</v>
+        <v>812200.4067041029</v>
       </c>
       <c r="B91" t="n">
-        <v>780817.2332511168</v>
+        <v>808605.2190970548</v>
       </c>
       <c r="C91" t="n">
-        <v>780827.2822388448</v>
+        <v>808640.2686542328</v>
       </c>
       <c r="D91" t="n">
-        <v>784387.4202887148</v>
+        <v>816350.4000332424</v>
       </c>
       <c r="E91" t="n">
-        <v>2.34612226486206</v>
+        <v>2.46490120887756</v>
       </c>
       <c r="F91" t="n">
-        <v>3.00009560585022</v>
+        <v>2.87028527259826</v>
       </c>
       <c r="G91" t="n">
-        <v>2.92627596855163</v>
+        <v>2.83278155326843</v>
       </c>
       <c r="H91" t="n">
-        <v>2.35931324958801</v>
+        <v>2.47467327117919</v>
       </c>
       <c r="I91" t="n">
-        <v>1219.59899659911</v>
+        <v>1254.8649684515</v>
       </c>
       <c r="J91" t="n">
-        <v>1216.09907310229</v>
+        <v>1254.98061214218</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>784407.4210642752</v>
+        <v>816390.4015843632</v>
       </c>
       <c r="B92" t="n">
-        <v>784542.2346995472</v>
+        <v>812795.2381772712</v>
       </c>
       <c r="C92" t="n">
-        <v>784550.8450890359</v>
+        <v>812830.2635344933</v>
       </c>
       <c r="D92" t="n">
-        <v>788130.9839144665</v>
+        <v>820540.3949134992</v>
       </c>
       <c r="E92" t="n">
-        <v>2.35862612724304</v>
+        <v>2.47392892837524</v>
       </c>
       <c r="F92" t="n">
-        <v>2.99284172058105</v>
+        <v>2.88467621803283</v>
       </c>
       <c r="G92" t="n">
-        <v>2.99356651306152</v>
+        <v>2.8567726612091</v>
       </c>
       <c r="H92" t="n">
-        <v>2.36862897872924</v>
+        <v>2.4885869026184</v>
       </c>
       <c r="I92" t="n">
-        <v>1222.49965949914</v>
+        <v>1268.57675290219</v>
       </c>
       <c r="J92" t="n">
-        <v>1219.59900124416</v>
+        <v>1268.92480634692</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>820580.3964646236</v>
+      </c>
+      <c r="B93" t="n">
+        <v>816985.2330575316</v>
+      </c>
+      <c r="C93" t="n">
+        <v>817020.25841475</v>
+      </c>
+      <c r="D93" t="n">
+        <v>824730.3897937596</v>
+      </c>
+      <c r="E93" t="n">
+        <v>2.48751807212829</v>
+      </c>
+      <c r="F93" t="n">
+        <v>2.90145254135131</v>
+      </c>
+      <c r="G93" t="n">
+        <v>2.88616490364074</v>
+      </c>
+      <c r="H93" t="n">
+        <v>2.50597405433654</v>
+      </c>
+      <c r="I93" t="n">
+        <v>1282.28858636821</v>
+      </c>
+      <c r="J93" t="n">
+        <v>1282.86905473802</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>824770.3913448805</v>
+      </c>
+      <c r="B94" t="n">
+        <v>821175.2279377885</v>
+      </c>
+      <c r="C94" t="n">
+        <v>821210.2532949996</v>
+      </c>
+      <c r="D94" t="n">
+        <v>828960.3862251408</v>
+      </c>
+      <c r="E94" t="n">
+        <v>2.50446629524231</v>
+      </c>
+      <c r="F94" t="n">
+        <v>2.91939330101013</v>
+      </c>
+      <c r="G94" t="n">
+        <v>2.92265272140502</v>
+      </c>
+      <c r="H94" t="n">
+        <v>2.52464008331298</v>
+      </c>
+      <c r="I94" t="n">
+        <v>1296.00046444577</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1296.81334563021</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>829000.3877762615</v>
+      </c>
+      <c r="B95" t="n">
+        <v>825405.20016921</v>
+      </c>
+      <c r="C95" t="n">
+        <v>825440.2497263736</v>
+      </c>
+      <c r="D95" t="n">
+        <v>833150.381105394</v>
+      </c>
+      <c r="E95" t="n">
+        <v>2.52324676513671</v>
+      </c>
+      <c r="F95" t="n">
+        <v>2.94195294380188</v>
+      </c>
+      <c r="G95" t="n">
+        <v>2.89824628829956</v>
+      </c>
+      <c r="H95" t="n">
+        <v>2.54782938957214</v>
+      </c>
+      <c r="I95" t="n">
+        <v>1310.64195619645</v>
+      </c>
+      <c r="J95" t="n">
+        <v>1310.75760094126</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>833190.3826565184</v>
+      </c>
+      <c r="B96" t="n">
+        <v>829595.21924943</v>
+      </c>
+      <c r="C96" t="n">
+        <v>829630.2446066268</v>
+      </c>
+      <c r="D96" t="n">
+        <v>837340.3759856436</v>
+      </c>
+      <c r="E96" t="n">
+        <v>2.54605436325073</v>
+      </c>
+      <c r="F96" t="n">
+        <v>2.95787048339843</v>
+      </c>
+      <c r="G96" t="n">
+        <v>2.92557716369628</v>
+      </c>
+      <c r="H96" t="n">
+        <v>2.57346177101135</v>
+      </c>
+      <c r="I96" t="n">
+        <v>1324.35382618845</v>
+      </c>
+      <c r="J96" t="n">
+        <v>1324.70188284414</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>837380.377536768</v>
+      </c>
+      <c r="B97" t="n">
+        <v>833785.2141296867</v>
+      </c>
+      <c r="C97" t="n">
+        <v>833820.23948688</v>
+      </c>
+      <c r="D97" t="n">
+        <v>841530.3708659004</v>
+      </c>
+      <c r="E97" t="n">
+        <v>2.57183957099914</v>
+      </c>
+      <c r="F97" t="n">
+        <v>2.97300553321838</v>
+      </c>
+      <c r="G97" t="n">
+        <v>2.95451140403747</v>
+      </c>
+      <c r="H97" t="n">
+        <v>2.59985756874084</v>
+      </c>
+      <c r="I97" t="n">
+        <v>1338.0656730101</v>
+      </c>
+      <c r="J97" t="n">
+        <v>1338.64613894658</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>841570.3724170248</v>
+      </c>
+      <c r="B98" t="n">
+        <v>837975.2090099509</v>
+      </c>
+      <c r="C98" t="n">
+        <v>838010.2343671405</v>
+      </c>
+      <c r="D98" t="n">
+        <v>845713.6725543336</v>
+      </c>
+      <c r="E98" t="n">
+        <v>2.59810161590576</v>
+      </c>
+      <c r="F98" t="n">
+        <v>2.98731994628906</v>
+      </c>
+      <c r="G98" t="n">
+        <v>2.98838782310485</v>
+      </c>
+      <c r="H98" t="n">
+        <v>2.61789369583129</v>
+      </c>
+      <c r="I98" t="n">
+        <v>1351.77744407663</v>
+      </c>
+      <c r="J98" t="n">
+        <v>1352.59032129336</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>845753.6741054581</v>
+      </c>
+      <c r="B99" t="n">
+        <v>842158.4862984049</v>
+      </c>
+      <c r="C99" t="n">
+        <v>842193.5360555843</v>
+      </c>
+      <c r="D99" t="n">
+        <v>849777.4679888015</v>
+      </c>
+      <c r="E99" t="n">
+        <v>2.6163477897644</v>
+      </c>
+      <c r="F99" t="n">
+        <v>3.00003123283386</v>
+      </c>
+      <c r="G99" t="n">
+        <v>2.9532516002655</v>
+      </c>
+      <c r="H99" t="n">
+        <v>2.63178825378418</v>
+      </c>
+      <c r="I99" t="n">
+        <v>1365.44937447871</v>
+      </c>
+      <c r="J99" t="n">
+        <v>1365.44937912671</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>849817.2775401612</v>
+      </c>
+      <c r="B100" t="n">
+        <v>846188.4993741504</v>
+      </c>
+      <c r="C100" t="n">
+        <v>846217.3299389316</v>
+      </c>
+      <c r="D100" t="n">
+        <v>853757.9893250064</v>
+      </c>
+      <c r="E100" t="n">
+        <v>2.63018488883972</v>
+      </c>
+      <c r="F100" t="n">
+        <v>2.9948399066925</v>
+      </c>
+      <c r="G100" t="n">
+        <v>2.99995493888855</v>
+      </c>
+      <c r="H100" t="n">
+        <v>2.64434671401977</v>
+      </c>
+      <c r="I100" t="n">
+        <v>1375.32695446674</v>
+      </c>
+      <c r="J100" t="n">
+        <v>1376.11207001509</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>853797.9908761309</v>
+      </c>
+      <c r="B101" t="n">
+        <v>850207.8030629652</v>
+      </c>
+      <c r="C101" t="n">
+        <v>850237.8528262571</v>
+      </c>
+      <c r="D101" t="n">
+        <v>857698.0051107276</v>
+      </c>
+      <c r="E101" t="n">
+        <v>2.64285802841186</v>
+      </c>
+      <c r="F101" t="n">
+        <v>2.99982118606567</v>
+      </c>
+      <c r="G101" t="n">
+        <v>2.96098136901855</v>
+      </c>
+      <c r="H101" t="n">
+        <v>2.65688610076904</v>
+      </c>
+      <c r="I101" t="n">
+        <v>1385.17622873565</v>
+      </c>
+      <c r="J101" t="n">
+        <v>1385.1880859789</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>857738.0066618556</v>
+      </c>
+      <c r="B102" t="n">
+        <v>854152.8130425853</v>
+      </c>
+      <c r="C102" t="n">
+        <v>854177.8686119604</v>
+      </c>
+      <c r="D102" t="n">
+        <v>861642.5958908388</v>
+      </c>
+      <c r="E102" t="n">
+        <v>2.6555118560791</v>
+      </c>
+      <c r="F102" t="n">
+        <v>2.99541234970092</v>
+      </c>
+      <c r="G102" t="n">
+        <v>2.98020100593566</v>
+      </c>
+      <c r="H102" t="n">
+        <v>2.66585659980773</v>
+      </c>
+      <c r="I102" t="n">
+        <v>1393.09014832534</v>
+      </c>
+      <c r="J102" t="n">
+        <v>1393.43891118104</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>861682.5974419597</v>
+      </c>
+      <c r="B103" t="n">
+        <v>858087.4096349101</v>
+      </c>
+      <c r="C103" t="n">
+        <v>858122.4593920896</v>
+      </c>
+      <c r="D103" t="n">
+        <v>865546.5261206377</v>
+      </c>
+      <c r="E103" t="n">
+        <v>2.66436791419982</v>
+      </c>
+      <c r="F103" t="n">
+        <v>3.00001215934753</v>
+      </c>
+      <c r="G103" t="n">
+        <v>2.95821404457092</v>
+      </c>
+      <c r="H103" t="n">
+        <v>2.67728900909423</v>
+      </c>
+      <c r="I103" t="n">
+        <v>1400.98261346064</v>
+      </c>
+      <c r="J103" t="n">
+        <v>1400.98261810903</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>865586.5276717619</v>
+      </c>
+      <c r="B104" t="n">
+        <v>861991.3398647124</v>
+      </c>
+      <c r="C104" t="n">
+        <v>862026.3896218884</v>
+      </c>
+      <c r="D104" t="n">
+        <v>869408.2748019779</v>
+      </c>
+      <c r="E104" t="n">
+        <v>2.67559027671814</v>
+      </c>
+      <c r="F104" t="n">
+        <v>3.00006937980651</v>
+      </c>
+      <c r="G104" t="n">
+        <v>2.95928287506103</v>
+      </c>
+      <c r="H104" t="n">
+        <v>2.68738532066345</v>
+      </c>
+      <c r="I104" t="n">
+        <v>1408.04615231276</v>
+      </c>
+      <c r="J104" t="n">
+        <v>1408.04615696087</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>869448.2763530988</v>
+      </c>
+      <c r="B105" t="n">
+        <v>865861.3467359567</v>
+      </c>
+      <c r="C105" t="n">
+        <v>865888.1383032288</v>
+      </c>
+      <c r="D105" t="n">
+        <v>873271.8198811332</v>
+      </c>
+      <c r="E105" t="n">
+        <v>2.6860876083374</v>
+      </c>
+      <c r="F105" t="n">
+        <v>2.99079370498657</v>
+      </c>
+      <c r="G105" t="n">
+        <v>2.98178505897522</v>
+      </c>
+      <c r="H105" t="n">
+        <v>2.69689011573791</v>
+      </c>
+      <c r="I105" t="n">
+        <v>1414.2051238426</v>
+      </c>
+      <c r="J105" t="n">
+        <v>1414.59422913876</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>873311.8214322575</v>
+      </c>
+      <c r="B106" t="n">
+        <v>869723.0954172972</v>
+      </c>
+      <c r="C106" t="n">
+        <v>869751.683382366</v>
+      </c>
+      <c r="D106" t="n">
+        <v>877132.3679639208</v>
+      </c>
+      <c r="E106" t="n">
+        <v>2.6955349445343</v>
+      </c>
+      <c r="F106" t="n">
+        <v>2.98836970329284</v>
+      </c>
+      <c r="G106" t="n">
+        <v>2.98222398757934</v>
+      </c>
+      <c r="H106" t="n">
+        <v>2.70677661895752</v>
+      </c>
+      <c r="I106" t="n">
+        <v>1420.28835647759</v>
+      </c>
+      <c r="J106" t="n">
+        <v>1420.71921385594</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>877172.3695150452</v>
+      </c>
+      <c r="B107" t="n">
+        <v>873586.6404964523</v>
+      </c>
+      <c r="C107" t="n">
+        <v>873612.2314651716</v>
+      </c>
+      <c r="D107" t="n">
+        <v>880956.1224916921</v>
+      </c>
+      <c r="E107" t="n">
+        <v>2.70544052124023</v>
+      </c>
+      <c r="F107" t="n">
+        <v>2.99640488624572</v>
+      </c>
+      <c r="G107" t="n">
+        <v>2.97172689437866</v>
+      </c>
+      <c r="H107" t="n">
+        <v>2.71702575683593</v>
+      </c>
+      <c r="I107" t="n">
+        <v>1426.41331790345</v>
+      </c>
+      <c r="J107" t="n">
+        <v>1426.54211063111</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>880996.1240428165</v>
+      </c>
+      <c r="B108" t="n">
+        <v>877407.1870281299</v>
+      </c>
+      <c r="C108" t="n">
+        <v>877435.985992932</v>
+      </c>
+      <c r="D108" t="n">
+        <v>884776.5856234907</v>
+      </c>
+      <c r="E108" t="n">
+        <v>2.71555614471435</v>
+      </c>
+      <c r="F108" t="n">
+        <v>2.98554491996765</v>
+      </c>
+      <c r="G108" t="n">
+        <v>2.98314023017883</v>
+      </c>
+      <c r="H108" t="n">
+        <v>2.72549986839294</v>
+      </c>
+      <c r="I108" t="n">
+        <v>1431.53901189989</v>
+      </c>
+      <c r="J108" t="n">
+        <v>1431.97477437747</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>884816.5871746116</v>
+      </c>
+      <c r="B109" t="n">
+        <v>881230.9415559048</v>
+      </c>
+      <c r="C109" t="n">
+        <v>881256.4491247416</v>
+      </c>
+      <c r="D109" t="n">
+        <v>888600.7797507144</v>
+      </c>
+      <c r="E109" t="n">
+        <v>2.72425937652587</v>
+      </c>
+      <c r="F109" t="n">
+        <v>2.98718643188476</v>
+      </c>
+      <c r="G109" t="n">
+        <v>2.98357915878295</v>
+      </c>
+      <c r="H109" t="n">
+        <v>2.73301982879638</v>
+      </c>
+      <c r="I109" t="n">
+        <v>1436.73925229139</v>
+      </c>
+      <c r="J109" t="n">
+        <v>1437.09851859442</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>888640.7813018352</v>
+      </c>
+      <c r="B110" t="n">
+        <v>885050.5934886768</v>
+      </c>
+      <c r="C110" t="n">
+        <v>885080.6432519653</v>
+      </c>
+      <c r="D110" t="n">
+        <v>892384.9913267855</v>
+      </c>
+      <c r="E110" t="n">
+        <v>2.73181724548339</v>
+      </c>
+      <c r="F110" t="n">
+        <v>2.99642395973205</v>
+      </c>
+      <c r="G110" t="n">
+        <v>2.97023820877075</v>
+      </c>
+      <c r="H110" t="n">
+        <v>2.74092125892639</v>
+      </c>
+      <c r="I110" t="n">
+        <v>1441.86299142762</v>
+      </c>
+      <c r="J110" t="n">
+        <v>1441.96035002498</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>892424.99287791</v>
+      </c>
+      <c r="B111" t="n">
+        <v>888835.5972637883</v>
+      </c>
+      <c r="C111" t="n">
+        <v>888864.8548280364</v>
+      </c>
+      <c r="D111" t="n">
+        <v>896165.1415078487</v>
+      </c>
+      <c r="E111" t="n">
+        <v>2.7398715019226</v>
+      </c>
+      <c r="F111" t="n">
+        <v>2.98176598548889</v>
+      </c>
+      <c r="G111" t="n">
+        <v>2.98438072204589</v>
+      </c>
+      <c r="H111" t="n">
+        <v>2.74834561347961</v>
+      </c>
+      <c r="I111" t="n">
+        <v>1446.14381916982</v>
+      </c>
+      <c r="J111" t="n">
+        <v>1446.59023887122</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>896205.1430589696</v>
+      </c>
+      <c r="B112" t="n">
+        <v>892619.8088398704</v>
+      </c>
+      <c r="C112" t="n">
+        <v>892645.0050090924</v>
+      </c>
+      <c r="D112" t="n">
+        <v>899946.9164868947</v>
+      </c>
+      <c r="E112" t="n">
+        <v>2.74744868278503</v>
+      </c>
+      <c r="F112" t="n">
+        <v>2.9741506576538</v>
+      </c>
+      <c r="G112" t="n">
+        <v>2.99816799163818</v>
+      </c>
+      <c r="H112" t="n">
+        <v>2.75389957427978</v>
+      </c>
+      <c r="I112" t="n">
+        <v>1450.42507465069</v>
+      </c>
+      <c r="J112" t="n">
+        <v>1451.00951834007</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>899986.9180380156</v>
+      </c>
+      <c r="B113" t="n">
+        <v>896399.9590209228</v>
+      </c>
+      <c r="C113" t="n">
+        <v>896426.7799881456</v>
+      </c>
+      <c r="D113" t="n">
+        <v>903728.031666768</v>
+      </c>
+      <c r="E113" t="n">
+        <v>2.75296449661254</v>
+      </c>
+      <c r="F113" t="n">
+        <v>2.97105884552002</v>
+      </c>
+      <c r="G113" t="n">
+        <v>2.99792742729187</v>
+      </c>
+      <c r="H113" t="n">
+        <v>2.75830841064453</v>
+      </c>
+      <c r="I113" t="n">
+        <v>1454.6119284918</v>
+      </c>
+      <c r="J113" t="n">
+        <v>1455.23413104378</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>903768.0332178888</v>
+      </c>
+      <c r="B114" t="n">
+        <v>900181.7339999725</v>
+      </c>
+      <c r="C114" t="n">
+        <v>900207.8951680189</v>
+      </c>
+      <c r="D114" t="n">
+        <v>907508.580047334</v>
+      </c>
+      <c r="E114" t="n">
+        <v>2.75723981857299</v>
+      </c>
+      <c r="F114" t="n">
+        <v>2.97716617584228</v>
+      </c>
+      <c r="G114" t="n">
+        <v>2.99043107032775</v>
+      </c>
+      <c r="H114" t="n">
+        <v>2.76445412635803</v>
+      </c>
+      <c r="I114" t="n">
+        <v>1458.83654296663</v>
+      </c>
+      <c r="J114" t="n">
+        <v>1459.32720630489</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>907548.5815984549</v>
+      </c>
+      <c r="B115" t="n">
+        <v>903962.8491798419</v>
+      </c>
+      <c r="C115" t="n">
+        <v>903988.4435485812</v>
+      </c>
+      <c r="D115" t="n">
+        <v>911291.8342245839</v>
+      </c>
+      <c r="E115" t="n">
+        <v>2.76342344284057</v>
+      </c>
+      <c r="F115" t="n">
+        <v>2.98850321769714</v>
+      </c>
+      <c r="G115" t="n">
+        <v>2.98134613037109</v>
+      </c>
+      <c r="H115" t="n">
+        <v>2.76832866668701</v>
+      </c>
+      <c r="I115" t="n">
+        <v>1463.04584737967</v>
+      </c>
+      <c r="J115" t="n">
+        <v>1463.29092571976</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>911331.6437759437</v>
+      </c>
+      <c r="B116" t="n">
+        <v>907703.3960092872</v>
+      </c>
+      <c r="C116" t="n">
+        <v>907731.696174714</v>
+      </c>
+      <c r="D116" t="n">
+        <v>915034.7860510752</v>
+      </c>
+      <c r="E116" t="n">
+        <v>2.76743149757385</v>
+      </c>
+      <c r="F116" t="n">
+        <v>2.95966458320617</v>
+      </c>
+      <c r="G116" t="n">
+        <v>2.99989748001098</v>
+      </c>
+      <c r="H116" t="n">
+        <v>2.77462697029113</v>
+      </c>
+      <c r="I116" t="n">
+        <v>1466.31232910608</v>
+      </c>
+      <c r="J116" t="n">
+        <v>1467.08512459904</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>915074.787602196</v>
+      </c>
+      <c r="B117" t="n">
+        <v>911486.6501865372</v>
+      </c>
+      <c r="C117" t="n">
+        <v>911514.649552326</v>
+      </c>
+      <c r="D117" t="n">
+        <v>918776.349679266</v>
+      </c>
+      <c r="E117" t="n">
+        <v>2.77359628677368</v>
+      </c>
+      <c r="F117" t="n">
+        <v>2.99064087867736</v>
+      </c>
+      <c r="G117" t="n">
+        <v>2.97836875915527</v>
+      </c>
+      <c r="H117" t="n">
+        <v>2.77907395362854</v>
+      </c>
+      <c r="I117" t="n">
+        <v>1470.57132930729</v>
+      </c>
+      <c r="J117" t="n">
+        <v>1470.75609479327</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>918816.3512303904</v>
+      </c>
+      <c r="B118" t="n">
+        <v>915229.6020130283</v>
+      </c>
+      <c r="C118" t="n">
+        <v>915256.2131805168</v>
+      </c>
+      <c r="D118" t="n">
+        <v>922517.4595080276</v>
+      </c>
+      <c r="E118" t="n">
+        <v>2.77829146385192</v>
+      </c>
+      <c r="F118" t="n">
+        <v>2.97949481010437</v>
+      </c>
+      <c r="G118" t="n">
+        <v>2.98665189743042</v>
+      </c>
+      <c r="H118" t="n">
+        <v>2.784761428833</v>
+      </c>
+      <c r="I118" t="n">
+        <v>1473.89366762306</v>
+      </c>
+      <c r="J118" t="n">
+        <v>1474.27857991003</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>922557.4610591483</v>
+      </c>
+      <c r="B119" t="n">
+        <v>918971.1656412228</v>
+      </c>
+      <c r="C119" t="n">
+        <v>918997.3230092784</v>
+      </c>
+      <c r="D119" t="n">
+        <v>926262.1693323647</v>
+      </c>
+      <c r="E119" t="n">
+        <v>2.78403615951538</v>
+      </c>
+      <c r="F119" t="n">
+        <v>2.97247123718261</v>
+      </c>
+      <c r="G119" t="n">
+        <v>2.99140429496765</v>
+      </c>
+      <c r="H119" t="n">
+        <v>2.78922772407531</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1477.18376412475</v>
+      </c>
+      <c r="J119" t="n">
+        <v>1477.67434070722</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>926302.1708834857</v>
+      </c>
+      <c r="B120" t="n">
+        <v>922712.2754699808</v>
+      </c>
+      <c r="C120" t="n">
+        <v>922742.0328336156</v>
+      </c>
+      <c r="D120" t="n">
+        <v>930006.5803570908</v>
+      </c>
+      <c r="E120" t="n">
+        <v>2.78846430778503</v>
+      </c>
+      <c r="F120" t="n">
+        <v>2.97355914115905</v>
+      </c>
+      <c r="G120" t="n">
+        <v>2.98718643188476</v>
+      </c>
+      <c r="H120" t="n">
+        <v>2.79188060760498</v>
+      </c>
+      <c r="I120" t="n">
+        <v>1480.46330035427</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1480.9213346283</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>930046.5819082116</v>
+      </c>
+      <c r="B121" t="n">
+        <v>926456.9852943181</v>
+      </c>
+      <c r="C121" t="n">
+        <v>926486.4438583379</v>
+      </c>
+      <c r="D121" t="n">
+        <v>933748.2515851489</v>
+      </c>
+      <c r="E121" t="n">
+        <v>2.79134607315063</v>
+      </c>
+      <c r="F121" t="n">
+        <v>2.98718643188476</v>
+      </c>
+      <c r="G121" t="n">
+        <v>2.9807162284851</v>
+      </c>
+      <c r="H121" t="n">
+        <v>2.79554510116577</v>
+      </c>
+      <c r="I121" t="n">
+        <v>1483.82652156996</v>
+      </c>
+      <c r="J121" t="n">
+        <v>1484.04520101303</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>933788.2531362732</v>
+      </c>
+      <c r="B122" t="n">
+        <v>930193.0653292235</v>
+      </c>
+      <c r="C122" t="n">
+        <v>930228.1150863817</v>
+      </c>
+      <c r="D122" t="n">
+        <v>937450.1618617931</v>
+      </c>
+      <c r="E122" t="n">
+        <v>2.79489612579345</v>
+      </c>
+      <c r="F122" t="n">
+        <v>3.00010752677917</v>
+      </c>
+      <c r="G122" t="n">
+        <v>2.9751431941986</v>
+      </c>
+      <c r="H122" t="n">
+        <v>2.80020213127136</v>
+      </c>
+      <c r="I122" t="n">
+        <v>1487.10533959219</v>
+      </c>
+      <c r="J122" t="n">
+        <v>1487.10534423987</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>937490.163412914</v>
+      </c>
+      <c r="B123" t="n">
+        <v>933903.0659959884</v>
+      </c>
+      <c r="C123" t="n">
+        <v>933930.025363044</v>
+      </c>
+      <c r="D123" t="n">
+        <v>941192.1146895121</v>
+      </c>
+      <c r="E123" t="n">
+        <v>2.79962944984436</v>
+      </c>
+      <c r="F123" t="n">
+        <v>2.96794772148132</v>
+      </c>
+      <c r="G123" t="n">
+        <v>2.99195790290832</v>
+      </c>
+      <c r="H123" t="n">
+        <v>2.80392384529113</v>
+      </c>
+      <c r="I123" t="n">
+        <v>1489.54570530529</v>
+      </c>
+      <c r="J123" t="n">
+        <v>1490.05492174277</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>941232.1162406328</v>
+      </c>
+      <c r="B124" t="n">
+        <v>937641.9284274707</v>
+      </c>
+      <c r="C124" t="n">
+        <v>937671.9781907629</v>
+      </c>
+      <c r="D124" t="n">
+        <v>944894.6155654381</v>
+      </c>
+      <c r="E124" t="n">
+        <v>2.80327486991882</v>
+      </c>
+      <c r="F124" t="n">
+        <v>2.99713015556335</v>
+      </c>
+      <c r="G124" t="n">
+        <v>2.97951388359069</v>
+      </c>
+      <c r="H124" t="n">
+        <v>2.80690121650695</v>
+      </c>
+      <c r="I124" t="n">
+        <v>1492.84389658555</v>
+      </c>
+      <c r="J124" t="n">
+        <v>1492.88923843859</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>944934.6171165588</v>
+      </c>
+      <c r="B125" t="n">
+        <v>941346.9291003444</v>
+      </c>
+      <c r="C125" t="n">
+        <v>941374.4790666852</v>
+      </c>
+      <c r="D125" t="n">
+        <v>948599.3740386097</v>
+      </c>
+      <c r="E125" t="n">
+        <v>2.80642390251159</v>
+      </c>
+      <c r="F125" t="n">
+        <v>2.97327280044555</v>
+      </c>
+      <c r="G125" t="n">
+        <v>2.98873233795166</v>
+      </c>
+      <c r="H125" t="n">
+        <v>2.81100463867187</v>
+      </c>
+      <c r="I125" t="n">
+        <v>1495.2133758444</v>
+      </c>
+      <c r="J125" t="n">
+        <v>1495.62010930164</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>948639.3755897341</v>
+      </c>
+      <c r="B126" t="n">
+        <v>945049.4299762704</v>
+      </c>
+      <c r="C126" t="n">
+        <v>945079.2375398496</v>
+      </c>
+      <c r="D126" t="n">
+        <v>952339.6840683384</v>
+      </c>
+      <c r="E126" t="n">
+        <v>2.8104510307312</v>
+      </c>
+      <c r="F126" t="n">
+        <v>2.9532516002655</v>
+      </c>
+      <c r="G126" t="n">
+        <v>2.99744653701782</v>
+      </c>
+      <c r="H126" t="n">
+        <v>2.81384849548339</v>
+      </c>
+      <c r="I126" t="n">
+        <v>1497.59563266558</v>
+      </c>
+      <c r="J126" t="n">
+        <v>1498.28724902434</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>952379.6856194593</v>
+      </c>
+      <c r="B127" t="n">
+        <v>948784.4978124095</v>
+      </c>
+      <c r="C127" t="n">
+        <v>948819.5475695784</v>
+      </c>
+      <c r="D127" t="n">
+        <v>956041.7243448241</v>
+      </c>
+      <c r="E127" t="n">
+        <v>2.81339025497436</v>
+      </c>
+      <c r="F127" t="n">
+        <v>3.00001215934753</v>
+      </c>
+      <c r="G127" t="n">
+        <v>2.97913217544555</v>
+      </c>
+      <c r="H127" t="n">
+        <v>2.81724572181701</v>
+      </c>
+      <c r="I127" t="n">
+        <v>1500.8509557632</v>
+      </c>
+      <c r="J127" t="n">
+        <v>1500.85096041106</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>956081.7258959485</v>
+      </c>
+      <c r="B128" t="n">
+        <v>952491.5380827864</v>
+      </c>
+      <c r="C128" t="n">
+        <v>952521.5878460748</v>
+      </c>
+      <c r="D128" t="n">
+        <v>959745.4710192324</v>
+      </c>
+      <c r="E128" t="n">
+        <v>2.81673049926757</v>
+      </c>
+      <c r="F128" t="n">
+        <v>2.99678659439086</v>
+      </c>
+      <c r="G128" t="n">
+        <v>2.98193764686584</v>
+      </c>
+      <c r="H128" t="n">
+        <v>2.82018494606018</v>
+      </c>
+      <c r="I128" t="n">
+        <v>1503.29128946617</v>
+      </c>
+      <c r="J128" t="n">
+        <v>1503.33869935895</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>959785.4725703532</v>
+      </c>
+      <c r="B129" t="n">
+        <v>956195.2847571948</v>
+      </c>
+      <c r="C129" t="n">
+        <v>956225.3345204832</v>
+      </c>
+      <c r="D129" t="n">
+        <v>963446.0692974947</v>
+      </c>
+      <c r="E129" t="n">
+        <v>2.81970787048339</v>
+      </c>
+      <c r="F129" t="n">
+        <v>2.99382829666137</v>
+      </c>
+      <c r="G129" t="n">
+        <v>2.98243403434753</v>
+      </c>
+      <c r="H129" t="n">
+        <v>2.82446026802063</v>
+      </c>
+      <c r="I129" t="n">
+        <v>1505.66283786768</v>
+      </c>
+      <c r="J129" t="n">
+        <v>1505.74990525718</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>963486.0708486191</v>
+      </c>
+      <c r="B130" t="n">
+        <v>959895.8830354572</v>
+      </c>
+      <c r="C130" t="n">
+        <v>959925.9327987275</v>
+      </c>
+      <c r="D130" t="n">
+        <v>967147.604974584</v>
+      </c>
+      <c r="E130" t="n">
+        <v>2.8238685131073</v>
+      </c>
+      <c r="F130" t="n">
+        <v>2.99915313720703</v>
+      </c>
+      <c r="G130" t="n">
+        <v>2.98281574249267</v>
+      </c>
+      <c r="H130" t="n">
+        <v>2.8278956413269</v>
+      </c>
+      <c r="I130" t="n">
+        <v>1508.07403284381</v>
+      </c>
+      <c r="J130" t="n">
+        <v>1508.0879305595</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>967187.6065257048</v>
+      </c>
+      <c r="B131" t="n">
+        <v>963592.4187186551</v>
+      </c>
+      <c r="C131" t="n">
+        <v>963627.4684758347</v>
+      </c>
+      <c r="D131" t="n">
+        <v>970810.8568984729</v>
+      </c>
+      <c r="E131" t="n">
+        <v>2.82741856575012</v>
+      </c>
+      <c r="F131" t="n">
+        <v>3.00018382072448</v>
+      </c>
+      <c r="G131" t="n">
+        <v>2.98176598548889</v>
+      </c>
+      <c r="H131" t="n">
+        <v>2.83243799209594</v>
+      </c>
+      <c r="I131" t="n">
+        <v>1510.33156750167</v>
+      </c>
+      <c r="J131" t="n">
+        <v>1510.33157214938</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>970850.8584495935</v>
+      </c>
+      <c r="B132" t="n">
+        <v>967262.4178342993</v>
+      </c>
+      <c r="C132" t="n">
+        <v>967290.7203997237</v>
+      </c>
+      <c r="D132" t="n">
+        <v>974515.0969722781</v>
+      </c>
+      <c r="E132" t="n">
+        <v>2.83199906349182</v>
+      </c>
+      <c r="F132" t="n">
+        <v>2.95017886161804</v>
+      </c>
+      <c r="G132" t="n">
+        <v>2.99760675430297</v>
+      </c>
+      <c r="H132" t="n">
+        <v>2.83614063262939</v>
+      </c>
+      <c r="I132" t="n">
+        <v>1511.84228080575</v>
+      </c>
+      <c r="J132" t="n">
+        <v>1512.49891984659</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>974555.0985233987</v>
+      </c>
+      <c r="B133" t="n">
+        <v>970965.6713093052</v>
+      </c>
+      <c r="C133" t="n">
+        <v>970994.9604735288</v>
+      </c>
+      <c r="D133" t="n">
+        <v>978215.9780501785</v>
+      </c>
+      <c r="E133" t="n">
+        <v>2.83570170402526</v>
+      </c>
+      <c r="F133" t="n">
+        <v>2.97441792488098</v>
+      </c>
+      <c r="G133" t="n">
+        <v>2.98886585235595</v>
+      </c>
+      <c r="H133" t="n">
+        <v>2.84114122390747</v>
+      </c>
+      <c r="I133" t="n">
+        <v>1514.24203042007</v>
+      </c>
+      <c r="J133" t="n">
+        <v>1514.57297724368</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>978255.9796012992</v>
+      </c>
+      <c r="B134" t="n">
+        <v>974660.7917942497</v>
+      </c>
+      <c r="C134" t="n">
+        <v>974695.8415514292</v>
+      </c>
+      <c r="D134" t="n">
+        <v>981877.4239762691</v>
+      </c>
+      <c r="E134" t="n">
+        <v>2.84053039550781</v>
+      </c>
+      <c r="F134" t="n">
+        <v>2.99993562698364</v>
+      </c>
+      <c r="G134" t="n">
+        <v>2.98392271995544</v>
+      </c>
+      <c r="H134" t="n">
+        <v>2.84572172164917</v>
+      </c>
+      <c r="I134" t="n">
+        <v>1516.56895505921</v>
+      </c>
+      <c r="J134" t="n">
+        <v>1516.56895970728</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>981917.4255273936</v>
+      </c>
+      <c r="B135" t="n">
+        <v>978330.7909098936</v>
+      </c>
+      <c r="C135" t="n">
+        <v>978357.2874775199</v>
+      </c>
+      <c r="D135" t="n">
+        <v>985580.5244514731</v>
+      </c>
+      <c r="E135" t="n">
+        <v>2.84514927864074</v>
+      </c>
+      <c r="F135" t="n">
+        <v>2.96934103965759</v>
+      </c>
+      <c r="G135" t="n">
+        <v>2.99159526824951</v>
+      </c>
+      <c r="H135" t="n">
+        <v>2.84955811500549</v>
+      </c>
+      <c r="I135" t="n">
+        <v>1518.07966076952</v>
+      </c>
+      <c r="J135" t="n">
+        <v>1518.46191289888</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>985620.3340028328</v>
+      </c>
+      <c r="B136" t="n">
+        <v>981992.2368359808</v>
+      </c>
+      <c r="C136" t="n">
+        <v>982020.3864016032</v>
+      </c>
+      <c r="D136" t="n">
+        <v>989245.3435734385</v>
+      </c>
+      <c r="E136" t="n">
+        <v>2.84917640686035</v>
+      </c>
+      <c r="F136" t="n">
+        <v>2.9368188381195</v>
+      </c>
+      <c r="G136" t="n">
+        <v>2.99995493888855</v>
+      </c>
+      <c r="H136" t="n">
+        <v>2.85402417182922</v>
+      </c>
+      <c r="I136" t="n">
+        <v>1519.50778198196</v>
+      </c>
+      <c r="J136" t="n">
+        <v>1520.27707110737</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>989285.3451245591</v>
+      </c>
+      <c r="B137" t="n">
+        <v>985695.1573114007</v>
+      </c>
+      <c r="C137" t="n">
+        <v>985725.2070746893</v>
+      </c>
+      <c r="D137" t="n">
+        <v>992906.9394993468</v>
+      </c>
+      <c r="E137" t="n">
+        <v>2.85358524322509</v>
+      </c>
+      <c r="F137" t="n">
+        <v>2.990736246109</v>
+      </c>
+      <c r="G137" t="n">
+        <v>2.9874153137207</v>
+      </c>
+      <c r="H137" t="n">
+        <v>2.85843300819397</v>
+      </c>
+      <c r="I137" t="n">
+        <v>1521.90397702408</v>
+      </c>
+      <c r="J137" t="n">
+        <v>1522.01600487448</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>992946.9410504713</v>
+      </c>
+      <c r="B138" t="n">
+        <v>989360.1564331499</v>
+      </c>
+      <c r="C138" t="n">
+        <v>989386.8030005796</v>
+      </c>
+      <c r="D138" t="n">
+        <v>996570.4040229708</v>
+      </c>
+      <c r="E138" t="n">
+        <v>2.85797500610351</v>
+      </c>
+      <c r="F138" t="n">
+        <v>2.97705173492431</v>
+      </c>
+      <c r="G138" t="n">
+        <v>2.99075531959533</v>
+      </c>
+      <c r="H138" t="n">
+        <v>2.86391067504882</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1523.41050342826</v>
+      </c>
+      <c r="J138" t="n">
+        <v>1523.68003607078</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>996610.4055740916</v>
+      </c>
+      <c r="B139" t="n">
+        <v>993021.752359062</v>
+      </c>
+      <c r="C139" t="n">
+        <v>993050.2675242214</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1000235.091745098</v>
+      </c>
+      <c r="E139" t="n">
+        <v>2.86349081993103</v>
+      </c>
+      <c r="F139" t="n">
+        <v>2.96292829513549</v>
+      </c>
+      <c r="G139" t="n">
+        <v>2.99283576011657</v>
+      </c>
+      <c r="H139" t="n">
+        <v>2.86898756027221</v>
+      </c>
+      <c r="I139" t="n">
+        <v>1524.8421202568</v>
+      </c>
+      <c r="J139" t="n">
+        <v>1525.27128663177</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>1000275.093296222</v>
+      </c>
+      <c r="B140" t="n">
+        <v>996685.2168826823</v>
+      </c>
+      <c r="C140" t="n">
+        <v>996714.9552463487</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1003896.537671185</v>
+      </c>
+      <c r="E140" t="n">
+        <v>2.86831951141357</v>
+      </c>
+      <c r="F140" t="n">
+        <v>2.95989346504211</v>
+      </c>
+      <c r="G140" t="n">
+        <v>2.9928548336029</v>
+      </c>
+      <c r="H140" t="n">
+        <v>2.87379717826843</v>
+      </c>
+      <c r="I140" t="n">
+        <v>1526.31716231533</v>
+      </c>
+      <c r="J140" t="n">
+        <v>1526.77475790627</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>1003936.539222306</v>
+      </c>
+      <c r="B141" t="n">
+        <v>1000349.90460481</v>
+      </c>
+      <c r="C141" t="n">
+        <v>1000376.401172436</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1007559.823195048</v>
+      </c>
+      <c r="E141" t="n">
+        <v>2.87352991104126</v>
+      </c>
+      <c r="F141" t="n">
+        <v>2.96603918075561</v>
+      </c>
+      <c r="G141" t="n">
+        <v>2.99321746826171</v>
+      </c>
+      <c r="H141" t="n">
+        <v>2.87870216369628</v>
+      </c>
+      <c r="I141" t="n">
+        <v>1527.82063394154</v>
+      </c>
+      <c r="J141" t="n">
+        <v>1528.20288761743</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>1007599.824746168</v>
+      </c>
+      <c r="B142" t="n">
+        <v>1004011.350530897</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1004039.68669628</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1011220.037922625</v>
+      </c>
+      <c r="E142" t="n">
+        <v>2.87833952903747</v>
+      </c>
+      <c r="F142" t="n">
+        <v>2.9721086025238</v>
+      </c>
+      <c r="G142" t="n">
+        <v>2.99212956428527</v>
+      </c>
+      <c r="H142" t="n">
+        <v>2.88477158546447</v>
+      </c>
+      <c r="I142" t="n">
+        <v>1529.24875776518</v>
+      </c>
+      <c r="J142" t="n">
+        <v>1529.55755687024</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>1011260.03947375</v>
+      </c>
+      <c r="B143" t="n">
+        <v>1007674.636054756</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1007699.901423876</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1014881.730848417</v>
+      </c>
+      <c r="E143" t="n">
+        <v>2.88417983055114</v>
+      </c>
+      <c r="F143" t="n">
+        <v>2.98878955841064</v>
+      </c>
+      <c r="G143" t="n">
+        <v>2.99148058891296</v>
+      </c>
+      <c r="H143" t="n">
+        <v>2.88939023017883</v>
+      </c>
+      <c r="I143" t="n">
+        <v>1530.71963640175</v>
+      </c>
+      <c r="J143" t="n">
+        <v>1530.84086289505</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>1014921.732399538</v>
+      </c>
+      <c r="B144" t="n">
+        <v>1011326.544592488</v>
+      </c>
+      <c r="C144" t="n">
+        <v>1011361.594349664</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1018505.642620385</v>
+      </c>
+      <c r="E144" t="n">
+        <v>2.88889408111572</v>
+      </c>
+      <c r="F144" t="n">
+        <v>3.00008845329284</v>
+      </c>
+      <c r="G144" t="n">
+        <v>2.99041199684143</v>
+      </c>
+      <c r="H144" t="n">
+        <v>2.89475345611572</v>
+      </c>
+      <c r="I144" t="n">
+        <v>1532.04231616839</v>
+      </c>
+      <c r="J144" t="n">
+        <v>1532.04232081643</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>1018545.644171506</v>
+      </c>
+      <c r="B145" t="n">
+        <v>1014956.542157008</v>
+      </c>
+      <c r="C145" t="n">
+        <v>1014985.506121628</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1022166.811946804</v>
+      </c>
+      <c r="E145" t="n">
+        <v>2.89444804191589</v>
+      </c>
+      <c r="F145" t="n">
+        <v>2.94765949249267</v>
+      </c>
+      <c r="G145" t="n">
+        <v>2.99489712715148</v>
+      </c>
+      <c r="H145" t="n">
+        <v>2.89895224571228</v>
+      </c>
+      <c r="I145" t="n">
+        <v>1532.62336591337</v>
+      </c>
+      <c r="J145" t="n">
+        <v>1533.17916581696</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>1022206.813497929</v>
+      </c>
+      <c r="B146" t="n">
+        <v>1018620.455480093</v>
+      </c>
+      <c r="C146" t="n">
+        <v>1018646.675448041</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1025790.660718834</v>
+      </c>
+      <c r="E146" t="n">
+        <v>2.89824628829956</v>
+      </c>
+      <c r="F146" t="n">
+        <v>2.98634648323059</v>
+      </c>
+      <c r="G146" t="n">
+        <v>2.9927213191986</v>
+      </c>
+      <c r="H146" t="n">
+        <v>2.90259766578674</v>
+      </c>
+      <c r="I146" t="n">
+        <v>1534.10882904274</v>
+      </c>
+      <c r="J146" t="n">
+        <v>1534.25224117422</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>1025830.662269954</v>
+      </c>
+      <c r="B147" t="n">
+        <v>1022241.623255395</v>
+      </c>
+      <c r="C147" t="n">
+        <v>1022270.524220084</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1029452.626044295</v>
+      </c>
+      <c r="E147" t="n">
+        <v>2.90213966369628</v>
+      </c>
+      <c r="F147" t="n">
+        <v>2.93584537506103</v>
+      </c>
+      <c r="G147" t="n">
+        <v>2.99768686294555</v>
+      </c>
+      <c r="H147" t="n">
+        <v>2.90517425537109</v>
+      </c>
+      <c r="I147" t="n">
+        <v>1534.60087823381</v>
+      </c>
+      <c r="J147" t="n">
+        <v>1535.27143199618</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>1029492.62759542</v>
+      </c>
+      <c r="B148" t="n">
+        <v>1025905.473578549</v>
+      </c>
+      <c r="C148" t="n">
+        <v>1025932.489545532</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1033073.119620421</v>
+      </c>
+      <c r="E148" t="n">
+        <v>2.9048306941986</v>
+      </c>
+      <c r="F148" t="n">
+        <v>2.98441886901855</v>
+      </c>
+      <c r="G148" t="n">
+        <v>2.9928548336029</v>
+      </c>
+      <c r="H148" t="n">
+        <v>2.90876245498657</v>
+      </c>
+      <c r="I148" t="n">
+        <v>1536.08489174566</v>
+      </c>
+      <c r="J148" t="n">
+        <v>1536.24680268275</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>1033113.121171545</v>
+      </c>
+      <c r="B149" t="n">
+        <v>1029527.437352886</v>
+      </c>
+      <c r="C149" t="n">
+        <v>1029552.983121665</v>
+      </c>
+      <c r="D149" t="n">
+        <v>1036736.884743696</v>
+      </c>
+      <c r="E149" t="n">
+        <v>2.90826630592346</v>
+      </c>
+      <c r="F149" t="n">
+        <v>2.94258260726928</v>
+      </c>
+      <c r="G149" t="n">
+        <v>2.99784731864929</v>
+      </c>
+      <c r="H149" t="n">
+        <v>2.91049933433532</v>
+      </c>
+      <c r="I149" t="n">
+        <v>1536.59543603545</v>
+      </c>
+      <c r="J149" t="n">
+        <v>1537.18800776408</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>1036776.886294817</v>
+      </c>
+      <c r="B150" t="n">
+        <v>1033186.698481655</v>
+      </c>
+      <c r="C150" t="n">
+        <v>1033216.748244929</v>
+      </c>
+      <c r="D150" t="n">
+        <v>1040359.58671712</v>
+      </c>
+      <c r="E150" t="n">
+        <v>2.90986943244934</v>
+      </c>
+      <c r="F150" t="n">
+        <v>2.99138522148132</v>
+      </c>
+      <c r="G150" t="n">
+        <v>2.99262595176696</v>
+      </c>
+      <c r="H150" t="n">
+        <v>2.91227436065673</v>
+      </c>
+      <c r="I150" t="n">
+        <v>1538.00146979782</v>
+      </c>
+      <c r="J150" t="n">
+        <v>1538.08900273956</v>
       </c>
     </row>
   </sheetData>
